--- a/finance_templates/donation_master.xlsx
+++ b/finance_templates/donation_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gyt_system\zhiban_cloud_system\finance_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC11AE94-FAE8-49A4-B079-571C87AE2064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D265EE9E-B0F0-4098-93CE-560E2F4E6C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,7 +392,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,18 +419,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -909,7 +897,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -1162,22 +1150,13 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="7" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1401,6 +1380,78 @@
     <xf numFmtId="178" fontId="25" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="178" fontId="25" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="7" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="5" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="18" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="7" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="5" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1418,63 +1469,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="7" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="7" borderId="18" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="7" borderId="18" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="7" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="7" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3742,12 +3736,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>472826</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>162568</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>669</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>66505</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3801610" cy="1015984"/>
+    <xdr:ext cx="3593883" cy="996707"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -3760,9 +3754,9 @@
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="20740141">
-          <a:off x="4054226" y="4163068"/>
-          <a:ext cx="3801610" cy="1015984"/>
+        <a:xfrm>
+          <a:off x="10226709" y="2520145"/>
+          <a:ext cx="3593883" cy="996707"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3790,7 +3784,7 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
+          <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
@@ -4117,9 +4111,9 @@
       <c r="O5" s="16"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="I6" s="189"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="191"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="211"/>
+      <c r="K6" s="212"/>
       <c r="L6" s="20"/>
       <c r="M6" s="3" t="s">
         <v>0</v>
@@ -4193,10 +4187,10 @@
       <c r="K8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L8" s="207"/>
-      <c r="M8" s="208"/>
-      <c r="N8" s="208"/>
-      <c r="O8" s="209"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="199"/>
+      <c r="N8" s="199"/>
+      <c r="O8" s="200"/>
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:19">
@@ -4211,10 +4205,10 @@
       <c r="I9" s="34"/>
       <c r="J9" s="34"/>
       <c r="K9" s="34"/>
-      <c r="L9" s="210"/>
-      <c r="M9" s="211"/>
-      <c r="N9" s="212"/>
-      <c r="O9" s="212"/>
+      <c r="L9" s="201"/>
+      <c r="M9" s="202"/>
+      <c r="N9" s="203"/>
+      <c r="O9" s="203"/>
       <c r="P9" s="38"/>
       <c r="R9" s="39"/>
       <c r="S9" s="39"/>
@@ -4231,10 +4225,10 @@
       <c r="I10" s="34"/>
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
-      <c r="L10" s="210"/>
-      <c r="M10" s="211"/>
-      <c r="N10" s="212"/>
-      <c r="O10" s="212"/>
+      <c r="L10" s="201"/>
+      <c r="M10" s="202"/>
+      <c r="N10" s="203"/>
+      <c r="O10" s="203"/>
       <c r="P10" s="38"/>
       <c r="R10" s="39"/>
       <c r="S10" s="39"/>
@@ -4251,10 +4245,10 @@
       <c r="I11" s="34"/>
       <c r="J11" s="34"/>
       <c r="K11" s="34"/>
-      <c r="L11" s="210"/>
-      <c r="M11" s="211"/>
-      <c r="N11" s="212"/>
-      <c r="O11" s="213"/>
+      <c r="L11" s="201"/>
+      <c r="M11" s="202"/>
+      <c r="N11" s="203"/>
+      <c r="O11" s="204"/>
       <c r="P11" s="38"/>
       <c r="R11" s="39"/>
       <c r="S11" s="39"/>
@@ -4271,10 +4265,10 @@
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
-      <c r="L12" s="210"/>
-      <c r="M12" s="211"/>
-      <c r="N12" s="212"/>
-      <c r="O12" s="212"/>
+      <c r="L12" s="201"/>
+      <c r="M12" s="202"/>
+      <c r="N12" s="203"/>
+      <c r="O12" s="203"/>
       <c r="P12" s="38"/>
       <c r="R12" s="39"/>
       <c r="S12" s="39"/>
@@ -4291,10 +4285,10 @@
       <c r="I13" s="34"/>
       <c r="J13" s="34"/>
       <c r="K13" s="34"/>
-      <c r="L13" s="210"/>
-      <c r="M13" s="211"/>
-      <c r="N13" s="212"/>
-      <c r="O13" s="212"/>
+      <c r="L13" s="201"/>
+      <c r="M13" s="202"/>
+      <c r="N13" s="203"/>
+      <c r="O13" s="203"/>
       <c r="P13" s="38"/>
       <c r="R13" s="39"/>
       <c r="S13" s="39"/>
@@ -4311,10 +4305,10 @@
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
       <c r="K14" s="34"/>
-      <c r="L14" s="210"/>
-      <c r="M14" s="211"/>
-      <c r="N14" s="212"/>
-      <c r="O14" s="212"/>
+      <c r="L14" s="201"/>
+      <c r="M14" s="202"/>
+      <c r="N14" s="203"/>
+      <c r="O14" s="203"/>
       <c r="P14" s="38"/>
       <c r="R14" s="39"/>
       <c r="S14" s="39"/>
@@ -4558,9 +4552,9 @@
     <col min="8" max="8" width="13.6640625" style="19" customWidth="1"/>
     <col min="9" max="9" width="10.88671875" style="19" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.44140625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="7.33203125" style="122" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" style="119" customWidth="1"/>
     <col min="12" max="12" width="15" style="19" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" style="120" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" style="117" customWidth="1"/>
     <col min="14" max="14" width="12.44140625" style="19" customWidth="1"/>
     <col min="15" max="16384" width="9.109375" style="16"/>
   </cols>
@@ -4589,11 +4583,11 @@
       <c r="E6" s="58"/>
       <c r="F6" s="58"/>
       <c r="G6" s="58"/>
-      <c r="H6" s="192" t="s">
+      <c r="H6" s="213" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="193"/>
-      <c r="J6" s="194"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="215"/>
       <c r="K6" s="61"/>
       <c r="L6" s="62" t="s">
         <v>19</v>
@@ -4682,11 +4676,11 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="88"/>
-      <c r="M9" s="89"/>
-      <c r="N9" s="90"/>
-      <c r="O9" s="91"/>
+      <c r="K9" s="205"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="189"/>
+      <c r="O9" s="90"/>
       <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:17" ht="15.6">
@@ -4700,15 +4694,15 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
-      <c r="K10" s="87"/>
-      <c r="L10" s="92"/>
-      <c r="M10" s="89"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="91"/>
+      <c r="K10" s="205"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="209"/>
+      <c r="O10" s="90"/>
       <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:17" ht="14.25" customHeight="1">
-      <c r="A11" s="94"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="81"/>
       <c r="C11" s="82"/>
       <c r="D11" s="83"/>
@@ -4718,33 +4712,33 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="91"/>
+      <c r="K11" s="190"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="209"/>
+      <c r="O11" s="90"/>
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:17" ht="15.6">
-      <c r="A12" s="94"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="81"/>
       <c r="C12" s="82"/>
-      <c r="D12" s="96"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="84"/>
       <c r="F12" s="85"/>
       <c r="G12" s="86"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="88"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="91"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="206"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="209"/>
+      <c r="O12" s="90"/>
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:17" ht="15.6">
-      <c r="A13" s="94"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="81"/>
       <c r="C13" s="82"/>
       <c r="D13" s="83"/>
@@ -4757,12 +4751,12 @@
       <c r="K13" s="87"/>
       <c r="L13" s="88"/>
       <c r="M13" s="89"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="91"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="90"/>
       <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:17" ht="15.6">
-      <c r="A14" s="94"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="81"/>
       <c r="C14" s="82"/>
       <c r="D14" s="83"/>
@@ -4775,12 +4769,12 @@
       <c r="K14" s="87"/>
       <c r="L14" s="88"/>
       <c r="M14" s="89"/>
-      <c r="N14" s="93"/>
-      <c r="O14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="90"/>
       <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:17" ht="15.6">
-      <c r="A15" s="94"/>
+      <c r="A15" s="92"/>
       <c r="B15" s="81"/>
       <c r="C15" s="75"/>
       <c r="D15" s="83"/>
@@ -4793,12 +4787,12 @@
       <c r="K15" s="87"/>
       <c r="L15" s="88"/>
       <c r="M15" s="89"/>
-      <c r="N15" s="93"/>
-      <c r="O15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="90"/>
       <c r="Q15" s="19"/>
     </row>
     <row r="16" spans="1:17" ht="15.6">
-      <c r="A16" s="97"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="81"/>
       <c r="C16" s="75"/>
       <c r="D16" s="83"/>
@@ -4811,12 +4805,12 @@
       <c r="K16" s="87"/>
       <c r="L16" s="88"/>
       <c r="M16" s="89"/>
-      <c r="N16" s="93"/>
-      <c r="O16" s="91"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="90"/>
       <c r="Q16" s="19"/>
     </row>
     <row r="17" spans="1:17" ht="15.6">
-      <c r="A17" s="97"/>
+      <c r="A17" s="94"/>
       <c r="B17" s="81"/>
       <c r="C17" s="82"/>
       <c r="D17" s="83"/>
@@ -4829,12 +4823,12 @@
       <c r="K17" s="87"/>
       <c r="L17" s="88"/>
       <c r="M17" s="89"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="90"/>
       <c r="Q17" s="19"/>
     </row>
     <row r="18" spans="1:17" ht="15.6">
-      <c r="A18" s="97"/>
+      <c r="A18" s="94"/>
       <c r="B18" s="81"/>
       <c r="C18" s="82"/>
       <c r="D18" s="83"/>
@@ -4847,12 +4841,12 @@
       <c r="K18" s="87"/>
       <c r="L18" s="88"/>
       <c r="M18" s="89"/>
-      <c r="N18" s="93"/>
-      <c r="O18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="90"/>
       <c r="Q18" s="19"/>
     </row>
     <row r="19" spans="1:17" ht="15.6">
-      <c r="A19" s="97"/>
+      <c r="A19" s="94"/>
       <c r="B19" s="81"/>
       <c r="C19" s="82"/>
       <c r="D19" s="83"/>
@@ -4865,12 +4859,12 @@
       <c r="K19" s="87"/>
       <c r="L19" s="88"/>
       <c r="M19" s="89"/>
-      <c r="N19" s="98"/>
-      <c r="O19" s="91"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="90"/>
       <c r="Q19" s="19"/>
     </row>
     <row r="20" spans="1:17" ht="15.6">
-      <c r="A20" s="97"/>
+      <c r="A20" s="94"/>
       <c r="B20" s="81"/>
       <c r="C20" s="82"/>
       <c r="D20" s="83"/>
@@ -4883,12 +4877,12 @@
       <c r="K20" s="87"/>
       <c r="L20" s="88"/>
       <c r="M20" s="89"/>
-      <c r="N20" s="98"/>
-      <c r="O20" s="91"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="90"/>
       <c r="Q20" s="19"/>
     </row>
     <row r="21" spans="1:17" ht="15.6">
-      <c r="A21" s="97"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="81"/>
       <c r="C21" s="82"/>
       <c r="D21" s="83"/>
@@ -4901,12 +4895,12 @@
       <c r="K21" s="87"/>
       <c r="L21" s="88"/>
       <c r="M21" s="89"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="90"/>
       <c r="Q21" s="19"/>
     </row>
     <row r="22" spans="1:17" ht="15.6">
-      <c r="A22" s="97"/>
+      <c r="A22" s="94"/>
       <c r="B22" s="81"/>
       <c r="C22" s="82"/>
       <c r="D22" s="83"/>
@@ -4919,14 +4913,14 @@
       <c r="K22" s="87"/>
       <c r="L22" s="88"/>
       <c r="M22" s="89"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="90"/>
       <c r="Q22" s="19"/>
     </row>
     <row r="23" spans="1:17" ht="15.6">
-      <c r="A23" s="97"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="81"/>
-      <c r="C23" s="200"/>
+      <c r="C23" s="191"/>
       <c r="D23" s="83"/>
       <c r="E23" s="84"/>
       <c r="F23" s="85"/>
@@ -4937,12 +4931,12 @@
       <c r="K23" s="87"/>
       <c r="L23" s="88"/>
       <c r="M23" s="89"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="99"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="96"/>
       <c r="Q23" s="19"/>
     </row>
     <row r="24" spans="1:17" ht="15.6">
-      <c r="A24" s="97"/>
+      <c r="A24" s="94"/>
       <c r="B24" s="81"/>
       <c r="C24" s="82"/>
       <c r="D24" s="83"/>
@@ -4955,12 +4949,12 @@
       <c r="K24" s="87"/>
       <c r="L24" s="88"/>
       <c r="M24" s="89"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="90"/>
       <c r="Q24" s="19"/>
     </row>
     <row r="25" spans="1:17" ht="15.6">
-      <c r="A25" s="97"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="81"/>
       <c r="C25" s="82"/>
       <c r="D25" s="83"/>
@@ -4970,17 +4964,17 @@
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
-      <c r="K25" s="100"/>
+      <c r="K25" s="97"/>
       <c r="L25" s="88"/>
       <c r="M25" s="89"/>
-      <c r="N25" s="101"/>
-      <c r="O25" s="91"/>
+      <c r="N25" s="98"/>
+      <c r="O25" s="90"/>
       <c r="Q25" s="19"/>
     </row>
     <row r="26" spans="1:17" ht="16.2">
-      <c r="A26" s="202"/>
-      <c r="B26" s="203"/>
-      <c r="C26" s="201"/>
+      <c r="A26" s="193"/>
+      <c r="B26" s="194"/>
+      <c r="C26" s="192"/>
       <c r="D26" s="83"/>
       <c r="E26" s="84"/>
       <c r="F26" s="85"/>
@@ -4988,16 +4982,16 @@
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="100"/>
+      <c r="K26" s="97"/>
       <c r="L26" s="88"/>
       <c r="M26" s="89"/>
-      <c r="N26" s="93"/>
-      <c r="O26" s="99"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="96"/>
       <c r="Q26" s="19"/>
     </row>
     <row r="27" spans="1:17" ht="15.6">
-      <c r="A27" s="204"/>
-      <c r="B27" s="205"/>
+      <c r="A27" s="195"/>
+      <c r="B27" s="196"/>
       <c r="C27" s="82"/>
       <c r="D27" s="83"/>
       <c r="E27" s="84"/>
@@ -5006,16 +5000,16 @@
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="100"/>
+      <c r="K27" s="97"/>
       <c r="L27" s="88"/>
       <c r="M27" s="89"/>
-      <c r="N27" s="98"/>
-      <c r="O27" s="91"/>
+      <c r="N27" s="95"/>
+      <c r="O27" s="90"/>
       <c r="Q27" s="19"/>
     </row>
     <row r="28" spans="1:17" ht="15.6">
-      <c r="A28" s="204"/>
-      <c r="B28" s="206"/>
+      <c r="A28" s="195"/>
+      <c r="B28" s="197"/>
       <c r="C28" s="82"/>
       <c r="D28" s="83"/>
       <c r="E28" s="84"/>
@@ -5024,15 +5018,15 @@
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
-      <c r="K28" s="199"/>
+      <c r="K28" s="190"/>
       <c r="L28" s="88"/>
       <c r="M28" s="89"/>
-      <c r="N28" s="198"/>
-      <c r="O28" s="91"/>
+      <c r="N28" s="189"/>
+      <c r="O28" s="90"/>
       <c r="Q28" s="19"/>
     </row>
     <row r="29" spans="1:17" ht="15.6">
-      <c r="A29" s="97"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="81"/>
       <c r="C29" s="82"/>
       <c r="D29" s="83"/>
@@ -5045,13 +5039,13 @@
       <c r="K29" s="87"/>
       <c r="L29" s="88"/>
       <c r="M29" s="89"/>
-      <c r="N29" s="93"/>
-      <c r="O29" s="91"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="90"/>
       <c r="Q29" s="19"/>
     </row>
     <row r="30" spans="1:17" ht="15.6">
-      <c r="A30" s="97"/>
-      <c r="B30" s="102"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="75"/>
       <c r="D30" s="83"/>
       <c r="E30" s="84"/>
@@ -5063,13 +5057,13 @@
       <c r="K30" s="87"/>
       <c r="L30" s="88"/>
       <c r="M30" s="89"/>
-      <c r="N30" s="93"/>
-      <c r="O30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="90"/>
       <c r="Q30" s="19"/>
     </row>
     <row r="31" spans="1:17" ht="15.6">
-      <c r="A31" s="97"/>
-      <c r="B31" s="102"/>
+      <c r="A31" s="94"/>
+      <c r="B31" s="99"/>
       <c r="C31" s="75"/>
       <c r="D31" s="83"/>
       <c r="E31" s="84"/>
@@ -5081,12 +5075,12 @@
       <c r="K31" s="87"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89"/>
-      <c r="N31" s="98"/>
-      <c r="O31" s="91"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="90"/>
       <c r="Q31" s="19"/>
     </row>
     <row r="32" spans="1:17" ht="15.6">
-      <c r="A32" s="97"/>
+      <c r="A32" s="94"/>
       <c r="B32" s="81"/>
       <c r="C32" s="75"/>
       <c r="D32" s="83"/>
@@ -5099,13 +5093,13 @@
       <c r="K32" s="87"/>
       <c r="L32" s="88"/>
       <c r="M32" s="89"/>
-      <c r="N32" s="98"/>
-      <c r="O32" s="91"/>
+      <c r="N32" s="95"/>
+      <c r="O32" s="90"/>
       <c r="Q32" s="19"/>
     </row>
     <row r="33" spans="1:17" ht="15.6">
-      <c r="A33" s="97"/>
-      <c r="B33" s="102"/>
+      <c r="A33" s="94"/>
+      <c r="B33" s="99"/>
       <c r="C33" s="75"/>
       <c r="D33" s="83"/>
       <c r="E33" s="84"/>
@@ -5116,13 +5110,13 @@
       <c r="J33" s="14"/>
       <c r="K33" s="87"/>
       <c r="M33" s="89"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="91"/>
+      <c r="N33" s="98"/>
+      <c r="O33" s="90"/>
       <c r="Q33" s="19"/>
     </row>
     <row r="34" spans="1:17" ht="15.6">
-      <c r="A34" s="97"/>
-      <c r="B34" s="102"/>
+      <c r="A34" s="94"/>
+      <c r="B34" s="99"/>
       <c r="C34" s="75"/>
       <c r="D34" s="83"/>
       <c r="E34" s="84"/>
@@ -5134,12 +5128,12 @@
       <c r="K34" s="87"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89"/>
-      <c r="N34" s="101"/>
-      <c r="O34" s="91"/>
+      <c r="N34" s="98"/>
+      <c r="O34" s="90"/>
       <c r="Q34" s="19"/>
     </row>
     <row r="35" spans="1:17" ht="15.6">
-      <c r="A35" s="97"/>
+      <c r="A35" s="94"/>
       <c r="B35" s="81"/>
       <c r="C35" s="82"/>
       <c r="D35" s="83"/>
@@ -5152,13 +5146,13 @@
       <c r="K35" s="87"/>
       <c r="L35" s="88"/>
       <c r="M35" s="89"/>
-      <c r="N35" s="101"/>
-      <c r="O35" s="91"/>
+      <c r="N35" s="98"/>
+      <c r="O35" s="90"/>
       <c r="Q35" s="19"/>
     </row>
     <row r="36" spans="1:17" ht="15.6">
-      <c r="A36" s="97"/>
-      <c r="B36" s="102"/>
+      <c r="A36" s="94"/>
+      <c r="B36" s="99"/>
       <c r="C36" s="82"/>
       <c r="D36" s="83"/>
       <c r="E36" s="84"/>
@@ -5170,13 +5164,13 @@
       <c r="K36" s="87"/>
       <c r="L36" s="88"/>
       <c r="M36" s="89"/>
-      <c r="N36" s="101"/>
-      <c r="O36" s="91"/>
+      <c r="N36" s="98"/>
+      <c r="O36" s="90"/>
       <c r="Q36" s="19"/>
     </row>
     <row r="37" spans="1:17" ht="15.6">
-      <c r="A37" s="97"/>
-      <c r="B37" s="102"/>
+      <c r="A37" s="94"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="75"/>
       <c r="D37" s="83"/>
       <c r="E37" s="84"/>
@@ -5188,12 +5182,12 @@
       <c r="K37" s="87"/>
       <c r="L37" s="88"/>
       <c r="M37" s="89"/>
-      <c r="N37" s="101"/>
-      <c r="O37" s="91"/>
+      <c r="N37" s="98"/>
+      <c r="O37" s="90"/>
       <c r="Q37" s="19"/>
     </row>
     <row r="38" spans="1:17" ht="15.6">
-      <c r="A38" s="97"/>
+      <c r="A38" s="94"/>
       <c r="B38" s="81"/>
       <c r="C38" s="75"/>
       <c r="D38" s="83"/>
@@ -5206,13 +5200,13 @@
       <c r="K38" s="87"/>
       <c r="L38" s="88"/>
       <c r="M38" s="89"/>
-      <c r="N38" s="101"/>
-      <c r="O38" s="91"/>
+      <c r="N38" s="98"/>
+      <c r="O38" s="90"/>
       <c r="Q38" s="19"/>
     </row>
     <row r="39" spans="1:17" ht="15.6">
-      <c r="A39" s="97"/>
-      <c r="B39" s="102"/>
+      <c r="A39" s="94"/>
+      <c r="B39" s="99"/>
       <c r="C39" s="75"/>
       <c r="D39" s="83"/>
       <c r="E39" s="84"/>
@@ -5224,13 +5218,13 @@
       <c r="K39" s="87"/>
       <c r="L39" s="88"/>
       <c r="M39" s="89"/>
-      <c r="N39" s="101"/>
-      <c r="O39" s="91"/>
+      <c r="N39" s="98"/>
+      <c r="O39" s="90"/>
       <c r="Q39" s="19"/>
     </row>
     <row r="40" spans="1:17" ht="15.6">
-      <c r="A40" s="97"/>
-      <c r="B40" s="102"/>
+      <c r="A40" s="94"/>
+      <c r="B40" s="99"/>
       <c r="C40" s="75"/>
       <c r="D40" s="83"/>
       <c r="E40" s="84"/>
@@ -5242,12 +5236,12 @@
       <c r="K40" s="87"/>
       <c r="L40" s="88"/>
       <c r="M40" s="89"/>
-      <c r="N40" s="101"/>
-      <c r="O40" s="91"/>
+      <c r="N40" s="98"/>
+      <c r="O40" s="90"/>
       <c r="Q40" s="19"/>
     </row>
     <row r="41" spans="1:17" ht="15.6">
-      <c r="A41" s="97"/>
+      <c r="A41" s="94"/>
       <c r="B41" s="81"/>
       <c r="C41" s="75"/>
       <c r="D41" s="83"/>
@@ -5260,13 +5254,13 @@
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
       <c r="M41" s="89"/>
-      <c r="N41" s="101"/>
-      <c r="O41" s="91"/>
+      <c r="N41" s="98"/>
+      <c r="O41" s="90"/>
       <c r="Q41" s="19"/>
     </row>
     <row r="42" spans="1:17" ht="15.6">
-      <c r="A42" s="97"/>
-      <c r="B42" s="102"/>
+      <c r="A42" s="94"/>
+      <c r="B42" s="99"/>
       <c r="C42" s="75"/>
       <c r="D42" s="83"/>
       <c r="E42" s="84"/>
@@ -5278,13 +5272,13 @@
       <c r="K42" s="87"/>
       <c r="L42" s="88"/>
       <c r="M42" s="89"/>
-      <c r="N42" s="101"/>
-      <c r="O42" s="91"/>
+      <c r="N42" s="98"/>
+      <c r="O42" s="90"/>
       <c r="Q42" s="19"/>
     </row>
     <row r="43" spans="1:17" ht="15.6">
-      <c r="A43" s="97"/>
-      <c r="B43" s="102"/>
+      <c r="A43" s="94"/>
+      <c r="B43" s="99"/>
       <c r="C43" s="75"/>
       <c r="D43" s="83"/>
       <c r="E43" s="84"/>
@@ -5296,13 +5290,13 @@
       <c r="K43" s="87"/>
       <c r="L43" s="88"/>
       <c r="M43" s="89"/>
-      <c r="N43" s="101"/>
-      <c r="O43" s="91"/>
+      <c r="N43" s="98"/>
+      <c r="O43" s="90"/>
       <c r="Q43" s="19"/>
     </row>
     <row r="44" spans="1:17" ht="15.6">
-      <c r="A44" s="97"/>
-      <c r="B44" s="102"/>
+      <c r="A44" s="94"/>
+      <c r="B44" s="99"/>
       <c r="C44" s="75"/>
       <c r="D44" s="83"/>
       <c r="E44" s="84"/>
@@ -5314,12 +5308,12 @@
       <c r="K44" s="87"/>
       <c r="L44" s="88"/>
       <c r="M44" s="89"/>
-      <c r="N44" s="101"/>
-      <c r="O44" s="91"/>
+      <c r="N44" s="98"/>
+      <c r="O44" s="90"/>
       <c r="Q44" s="19"/>
     </row>
     <row r="45" spans="1:17" ht="15.6">
-      <c r="A45" s="97"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="81"/>
       <c r="C45" s="75"/>
       <c r="D45" s="83"/>
@@ -5332,12 +5326,12 @@
       <c r="K45" s="87"/>
       <c r="L45" s="88"/>
       <c r="M45" s="89"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="91"/>
+      <c r="N45" s="98"/>
+      <c r="O45" s="90"/>
       <c r="Q45" s="19"/>
     </row>
     <row r="46" spans="1:17" ht="15.6">
-      <c r="A46" s="97"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="81"/>
       <c r="C46" s="75"/>
       <c r="D46" s="83"/>
@@ -5350,12 +5344,12 @@
       <c r="K46" s="87"/>
       <c r="L46" s="88"/>
       <c r="M46" s="89"/>
-      <c r="N46" s="101"/>
-      <c r="O46" s="91"/>
+      <c r="N46" s="98"/>
+      <c r="O46" s="90"/>
       <c r="Q46" s="19"/>
     </row>
     <row r="47" spans="1:17" ht="15.6">
-      <c r="A47" s="97"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="81"/>
       <c r="C47" s="75"/>
       <c r="D47" s="83"/>
@@ -5368,12 +5362,12 @@
       <c r="K47" s="87"/>
       <c r="L47" s="88"/>
       <c r="M47" s="89"/>
-      <c r="N47" s="101"/>
-      <c r="O47" s="91"/>
+      <c r="N47" s="98"/>
+      <c r="O47" s="90"/>
       <c r="Q47" s="19"/>
     </row>
     <row r="48" spans="1:17" ht="15.6">
-      <c r="A48" s="97"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="81"/>
       <c r="C48" s="75"/>
       <c r="D48" s="83"/>
@@ -5386,13 +5380,13 @@
       <c r="K48" s="87"/>
       <c r="L48" s="88"/>
       <c r="M48" s="89"/>
-      <c r="N48" s="101"/>
-      <c r="O48" s="91"/>
+      <c r="N48" s="98"/>
+      <c r="O48" s="90"/>
       <c r="Q48" s="19"/>
     </row>
     <row r="49" spans="1:17" ht="15.6">
-      <c r="A49" s="97"/>
-      <c r="B49" s="102"/>
+      <c r="A49" s="94"/>
+      <c r="B49" s="99"/>
       <c r="C49" s="75"/>
       <c r="D49" s="83"/>
       <c r="E49" s="84"/>
@@ -5404,12 +5398,12 @@
       <c r="K49" s="87"/>
       <c r="L49" s="88"/>
       <c r="M49" s="89"/>
-      <c r="N49" s="101"/>
-      <c r="O49" s="91"/>
+      <c r="N49" s="98"/>
+      <c r="O49" s="90"/>
       <c r="Q49" s="19"/>
     </row>
     <row r="50" spans="1:17" ht="15.6">
-      <c r="A50" s="97"/>
+      <c r="A50" s="94"/>
       <c r="B50" s="81"/>
       <c r="C50" s="82"/>
       <c r="D50" s="83"/>
@@ -5422,13 +5416,13 @@
       <c r="K50" s="87"/>
       <c r="L50" s="88"/>
       <c r="M50" s="89"/>
-      <c r="N50" s="101"/>
-      <c r="O50" s="91"/>
+      <c r="N50" s="98"/>
+      <c r="O50" s="90"/>
       <c r="Q50" s="19"/>
     </row>
     <row r="51" spans="1:17" ht="15.6">
-      <c r="A51" s="97"/>
-      <c r="B51" s="102"/>
+      <c r="A51" s="94"/>
+      <c r="B51" s="99"/>
       <c r="C51" s="82"/>
       <c r="D51" s="83"/>
       <c r="E51" s="84"/>
@@ -5440,12 +5434,12 @@
       <c r="K51" s="87"/>
       <c r="L51" s="88"/>
       <c r="M51" s="89"/>
-      <c r="N51" s="93"/>
-      <c r="O51" s="91"/>
+      <c r="N51" s="91"/>
+      <c r="O51" s="90"/>
       <c r="Q51" s="19"/>
     </row>
     <row r="52" spans="1:17" ht="15.6">
-      <c r="A52" s="97"/>
+      <c r="A52" s="94"/>
       <c r="B52" s="81"/>
       <c r="C52" s="75"/>
       <c r="D52" s="83"/>
@@ -5458,13 +5452,13 @@
       <c r="K52" s="87"/>
       <c r="L52" s="88"/>
       <c r="M52" s="89"/>
-      <c r="N52" s="93"/>
-      <c r="O52" s="91"/>
+      <c r="N52" s="91"/>
+      <c r="O52" s="90"/>
       <c r="Q52" s="19"/>
     </row>
     <row r="53" spans="1:17" ht="15.6">
-      <c r="A53" s="97"/>
-      <c r="B53" s="102"/>
+      <c r="A53" s="94"/>
+      <c r="B53" s="99"/>
       <c r="C53" s="75"/>
       <c r="D53" s="83"/>
       <c r="E53" s="84"/>
@@ -5476,12 +5470,12 @@
       <c r="K53" s="87"/>
       <c r="L53" s="88"/>
       <c r="M53" s="89"/>
-      <c r="N53" s="93"/>
-      <c r="O53" s="91"/>
+      <c r="N53" s="91"/>
+      <c r="O53" s="90"/>
       <c r="Q53" s="19"/>
     </row>
     <row r="54" spans="1:17" ht="15.6">
-      <c r="A54" s="97"/>
+      <c r="A54" s="94"/>
       <c r="B54" s="81"/>
       <c r="C54" s="75"/>
       <c r="D54" s="83"/>
@@ -5494,12 +5488,12 @@
       <c r="K54" s="87"/>
       <c r="L54" s="88"/>
       <c r="M54" s="89"/>
-      <c r="N54" s="103"/>
-      <c r="O54" s="91"/>
+      <c r="N54" s="100"/>
+      <c r="O54" s="90"/>
       <c r="Q54" s="19"/>
     </row>
     <row r="55" spans="1:17" ht="15.6">
-      <c r="A55" s="97"/>
+      <c r="A55" s="94"/>
       <c r="B55" s="81"/>
       <c r="C55" s="75"/>
       <c r="D55" s="83"/>
@@ -5512,13 +5506,13 @@
       <c r="K55" s="87"/>
       <c r="L55" s="88"/>
       <c r="M55" s="89"/>
-      <c r="N55" s="93"/>
-      <c r="O55" s="91"/>
+      <c r="N55" s="91"/>
+      <c r="O55" s="90"/>
       <c r="Q55" s="19"/>
     </row>
     <row r="56" spans="1:17" ht="15.6">
-      <c r="A56" s="97"/>
-      <c r="B56" s="102"/>
+      <c r="A56" s="94"/>
+      <c r="B56" s="99"/>
       <c r="C56" s="82"/>
       <c r="D56" s="83"/>
       <c r="E56" s="84"/>
@@ -5530,12 +5524,12 @@
       <c r="K56" s="87"/>
       <c r="L56" s="88"/>
       <c r="M56" s="89"/>
-      <c r="N56" s="101"/>
-      <c r="O56" s="91"/>
+      <c r="N56" s="98"/>
+      <c r="O56" s="90"/>
       <c r="Q56" s="19"/>
     </row>
     <row r="57" spans="1:17" ht="15.6">
-      <c r="A57" s="97"/>
+      <c r="A57" s="94"/>
       <c r="B57" s="81"/>
       <c r="C57" s="82"/>
       <c r="D57" s="83"/>
@@ -5548,13 +5542,13 @@
       <c r="K57" s="87"/>
       <c r="L57" s="88"/>
       <c r="M57" s="89"/>
-      <c r="N57" s="93"/>
-      <c r="O57" s="91"/>
+      <c r="N57" s="91"/>
+      <c r="O57" s="90"/>
       <c r="Q57" s="19"/>
     </row>
     <row r="58" spans="1:17" ht="15.6">
-      <c r="A58" s="97"/>
-      <c r="B58" s="102"/>
+      <c r="A58" s="94"/>
+      <c r="B58" s="99"/>
       <c r="C58" s="82"/>
       <c r="D58" s="83"/>
       <c r="E58" s="84"/>
@@ -5566,12 +5560,12 @@
       <c r="K58" s="87"/>
       <c r="L58" s="88"/>
       <c r="M58" s="89"/>
-      <c r="N58" s="93"/>
-      <c r="O58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="90"/>
       <c r="Q58" s="19"/>
     </row>
     <row r="59" spans="1:17" ht="15.6">
-      <c r="A59" s="97"/>
+      <c r="A59" s="94"/>
       <c r="B59" s="81"/>
       <c r="C59" s="82"/>
       <c r="D59" s="83"/>
@@ -5584,13 +5578,13 @@
       <c r="K59" s="87"/>
       <c r="L59" s="88"/>
       <c r="M59" s="89"/>
-      <c r="N59" s="93"/>
-      <c r="O59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="90"/>
       <c r="Q59" s="19"/>
     </row>
     <row r="60" spans="1:17" ht="15.6">
-      <c r="A60" s="97"/>
-      <c r="B60" s="102"/>
+      <c r="A60" s="94"/>
+      <c r="B60" s="99"/>
       <c r="C60" s="82"/>
       <c r="D60" s="83"/>
       <c r="E60" s="84"/>
@@ -5602,12 +5596,12 @@
       <c r="K60" s="87"/>
       <c r="L60" s="88"/>
       <c r="M60" s="89"/>
-      <c r="N60" s="93"/>
-      <c r="O60" s="91"/>
+      <c r="N60" s="91"/>
+      <c r="O60" s="90"/>
       <c r="Q60" s="19"/>
     </row>
     <row r="61" spans="1:17" ht="15.6">
-      <c r="A61" s="97"/>
+      <c r="A61" s="94"/>
       <c r="B61" s="81"/>
       <c r="C61" s="82"/>
       <c r="D61" s="83"/>
@@ -5620,13 +5614,13 @@
       <c r="K61" s="87"/>
       <c r="L61" s="88"/>
       <c r="M61" s="89"/>
-      <c r="N61" s="93"/>
-      <c r="O61" s="91"/>
+      <c r="N61" s="91"/>
+      <c r="O61" s="90"/>
       <c r="Q61" s="19"/>
     </row>
     <row r="62" spans="1:17" ht="15.6">
-      <c r="A62" s="97"/>
-      <c r="B62" s="102"/>
+      <c r="A62" s="94"/>
+      <c r="B62" s="99"/>
       <c r="C62" s="82"/>
       <c r="D62" s="83"/>
       <c r="E62" s="84"/>
@@ -5638,12 +5632,12 @@
       <c r="K62" s="87"/>
       <c r="L62" s="88"/>
       <c r="M62" s="89"/>
-      <c r="N62" s="93"/>
-      <c r="O62" s="91"/>
+      <c r="N62" s="91"/>
+      <c r="O62" s="90"/>
       <c r="Q62" s="19"/>
     </row>
     <row r="63" spans="1:17" ht="15.6">
-      <c r="A63" s="97"/>
+      <c r="A63" s="94"/>
       <c r="B63" s="81"/>
       <c r="C63" s="82"/>
       <c r="D63" s="83"/>
@@ -5656,13 +5650,13 @@
       <c r="K63" s="87"/>
       <c r="L63" s="88"/>
       <c r="M63" s="89"/>
-      <c r="N63" s="93"/>
-      <c r="O63" s="91"/>
+      <c r="N63" s="91"/>
+      <c r="O63" s="90"/>
       <c r="Q63" s="19"/>
     </row>
     <row r="64" spans="1:17" ht="15.6">
-      <c r="A64" s="97"/>
-      <c r="B64" s="102"/>
+      <c r="A64" s="94"/>
+      <c r="B64" s="99"/>
       <c r="C64" s="82"/>
       <c r="D64" s="83"/>
       <c r="E64" s="84"/>
@@ -5671,15 +5665,15 @@
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="14"/>
-      <c r="K64" s="100"/>
+      <c r="K64" s="97"/>
       <c r="L64" s="88"/>
       <c r="M64" s="89"/>
-      <c r="N64" s="98"/>
-      <c r="O64" s="91"/>
+      <c r="N64" s="95"/>
+      <c r="O64" s="90"/>
       <c r="Q64" s="19"/>
     </row>
     <row r="65" spans="1:17" ht="15.6">
-      <c r="A65" s="97"/>
+      <c r="A65" s="94"/>
       <c r="B65" s="81"/>
       <c r="C65" s="75"/>
       <c r="D65" s="83"/>
@@ -5692,13 +5686,13 @@
       <c r="K65" s="87"/>
       <c r="L65" s="88"/>
       <c r="M65" s="89"/>
-      <c r="N65" s="101"/>
-      <c r="O65" s="91"/>
+      <c r="N65" s="98"/>
+      <c r="O65" s="90"/>
       <c r="Q65" s="19"/>
     </row>
     <row r="66" spans="1:17" ht="15.6">
-      <c r="A66" s="97"/>
-      <c r="B66" s="102"/>
+      <c r="A66" s="94"/>
+      <c r="B66" s="99"/>
       <c r="C66" s="82"/>
       <c r="D66" s="83"/>
       <c r="E66" s="84"/>
@@ -5710,13 +5704,13 @@
       <c r="K66" s="87"/>
       <c r="L66" s="88"/>
       <c r="M66" s="89"/>
-      <c r="N66" s="93"/>
-      <c r="O66" s="91"/>
+      <c r="N66" s="91"/>
+      <c r="O66" s="90"/>
       <c r="Q66" s="19"/>
     </row>
     <row r="67" spans="1:17" ht="15.6">
-      <c r="A67" s="97"/>
-      <c r="B67" s="102"/>
+      <c r="A67" s="94"/>
+      <c r="B67" s="99"/>
       <c r="C67" s="82"/>
       <c r="D67" s="83"/>
       <c r="E67" s="84"/>
@@ -5728,13 +5722,13 @@
       <c r="K67" s="87"/>
       <c r="L67" s="88"/>
       <c r="M67" s="89"/>
-      <c r="N67" s="93"/>
-      <c r="O67" s="91"/>
+      <c r="N67" s="91"/>
+      <c r="O67" s="90"/>
       <c r="Q67" s="19"/>
     </row>
     <row r="68" spans="1:17" ht="15.6">
-      <c r="A68" s="97"/>
-      <c r="B68" s="102"/>
+      <c r="A68" s="94"/>
+      <c r="B68" s="99"/>
       <c r="C68" s="82"/>
       <c r="D68" s="83"/>
       <c r="E68" s="84"/>
@@ -5746,13 +5740,13 @@
       <c r="K68" s="87"/>
       <c r="L68" s="88"/>
       <c r="M68" s="89"/>
-      <c r="N68" s="93"/>
-      <c r="O68" s="91"/>
+      <c r="N68" s="91"/>
+      <c r="O68" s="90"/>
       <c r="Q68" s="19"/>
     </row>
     <row r="69" spans="1:17" ht="15.6">
-      <c r="A69" s="97"/>
-      <c r="B69" s="102"/>
+      <c r="A69" s="94"/>
+      <c r="B69" s="99"/>
       <c r="C69" s="75"/>
       <c r="D69" s="83"/>
       <c r="E69" s="84"/>
@@ -5764,13 +5758,13 @@
       <c r="K69" s="87"/>
       <c r="L69" s="88"/>
       <c r="M69" s="89"/>
-      <c r="N69" s="93"/>
-      <c r="O69" s="91"/>
+      <c r="N69" s="91"/>
+      <c r="O69" s="90"/>
       <c r="Q69" s="19"/>
     </row>
     <row r="70" spans="1:17" ht="15.6">
-      <c r="A70" s="97"/>
-      <c r="B70" s="102"/>
+      <c r="A70" s="94"/>
+      <c r="B70" s="99"/>
       <c r="C70" s="75"/>
       <c r="D70" s="83"/>
       <c r="E70" s="84"/>
@@ -5782,49 +5776,49 @@
       <c r="K70" s="87"/>
       <c r="L70" s="88"/>
       <c r="M70" s="89"/>
-      <c r="N70" s="93"/>
-      <c r="O70" s="91"/>
+      <c r="N70" s="91"/>
+      <c r="O70" s="90"/>
       <c r="Q70" s="19"/>
     </row>
     <row r="71" spans="1:17" ht="15.6">
-      <c r="A71" s="97"/>
-      <c r="B71" s="102"/>
+      <c r="A71" s="94"/>
+      <c r="B71" s="99"/>
       <c r="C71" s="75"/>
       <c r="D71" s="83"/>
       <c r="E71" s="84"/>
-      <c r="F71" s="104"/>
-      <c r="G71" s="105"/>
+      <c r="F71" s="101"/>
+      <c r="G71" s="102"/>
       <c r="H71" s="14"/>
       <c r="I71" s="14"/>
       <c r="J71" s="14"/>
-      <c r="K71" s="100"/>
+      <c r="K71" s="97"/>
       <c r="L71" s="88"/>
       <c r="M71" s="89"/>
-      <c r="N71" s="93"/>
-      <c r="O71" s="91"/>
+      <c r="N71" s="91"/>
+      <c r="O71" s="90"/>
       <c r="Q71" s="19"/>
     </row>
     <row r="72" spans="1:17" ht="15.6">
-      <c r="A72" s="97"/>
-      <c r="B72" s="102"/>
+      <c r="A72" s="94"/>
+      <c r="B72" s="99"/>
       <c r="C72" s="82"/>
       <c r="D72" s="83"/>
       <c r="E72" s="84"/>
-      <c r="F72" s="104"/>
-      <c r="G72" s="105"/>
+      <c r="F72" s="101"/>
+      <c r="G72" s="102"/>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14"/>
-      <c r="K72" s="106"/>
+      <c r="K72" s="103"/>
       <c r="L72" s="88"/>
       <c r="M72" s="89"/>
-      <c r="N72" s="93"/>
-      <c r="O72" s="91"/>
+      <c r="N72" s="91"/>
+      <c r="O72" s="90"/>
       <c r="Q72" s="19"/>
     </row>
     <row r="73" spans="1:17" ht="15.6">
-      <c r="A73" s="97"/>
-      <c r="B73" s="102"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="99"/>
       <c r="C73" s="75"/>
       <c r="D73" s="43"/>
       <c r="E73" s="30"/>
@@ -5836,13 +5830,13 @@
       <c r="K73" s="87"/>
       <c r="L73" s="88"/>
       <c r="M73" s="89"/>
-      <c r="N73" s="93"/>
-      <c r="O73" s="91"/>
+      <c r="N73" s="91"/>
+      <c r="O73" s="90"/>
       <c r="Q73" s="19"/>
     </row>
     <row r="74" spans="1:17" ht="15.6">
-      <c r="A74" s="97"/>
-      <c r="B74" s="102"/>
+      <c r="A74" s="94"/>
+      <c r="B74" s="99"/>
       <c r="C74" s="75"/>
       <c r="D74" s="43"/>
       <c r="E74" s="30"/>
@@ -5854,13 +5848,13 @@
       <c r="K74" s="87"/>
       <c r="L74" s="88"/>
       <c r="M74" s="89"/>
-      <c r="N74" s="93"/>
-      <c r="O74" s="91"/>
+      <c r="N74" s="91"/>
+      <c r="O74" s="90"/>
       <c r="Q74" s="19"/>
     </row>
     <row r="75" spans="1:17" ht="15.6">
-      <c r="A75" s="97"/>
-      <c r="B75" s="102"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="99"/>
       <c r="C75" s="75"/>
       <c r="D75" s="43"/>
       <c r="E75" s="30"/>
@@ -5872,13 +5866,13 @@
       <c r="K75" s="87"/>
       <c r="L75" s="88"/>
       <c r="M75" s="89"/>
-      <c r="N75" s="93"/>
-      <c r="O75" s="91"/>
+      <c r="N75" s="91"/>
+      <c r="O75" s="90"/>
       <c r="Q75" s="19"/>
     </row>
     <row r="76" spans="1:17" ht="15.6">
-      <c r="A76" s="97"/>
-      <c r="B76" s="102"/>
+      <c r="A76" s="94"/>
+      <c r="B76" s="99"/>
       <c r="C76" s="82"/>
       <c r="D76" s="83"/>
       <c r="E76" s="84"/>
@@ -5887,16 +5881,16 @@
       <c r="H76" s="14"/>
       <c r="I76" s="14"/>
       <c r="J76" s="14"/>
-      <c r="K76" s="100"/>
+      <c r="K76" s="97"/>
       <c r="L76" s="88"/>
       <c r="M76" s="89"/>
-      <c r="N76" s="93"/>
-      <c r="O76" s="91"/>
+      <c r="N76" s="91"/>
+      <c r="O76" s="90"/>
       <c r="Q76" s="19"/>
     </row>
     <row r="77" spans="1:17" ht="15.6">
-      <c r="A77" s="97"/>
-      <c r="B77" s="102"/>
+      <c r="A77" s="94"/>
+      <c r="B77" s="99"/>
       <c r="C77" s="75"/>
       <c r="D77" s="83"/>
       <c r="E77" s="84"/>
@@ -5908,13 +5902,13 @@
       <c r="K77" s="87"/>
       <c r="L77" s="88"/>
       <c r="M77" s="89"/>
-      <c r="N77" s="93"/>
-      <c r="O77" s="91"/>
+      <c r="N77" s="91"/>
+      <c r="O77" s="90"/>
       <c r="Q77" s="19"/>
     </row>
     <row r="78" spans="1:17" ht="15.6">
-      <c r="A78" s="97"/>
-      <c r="B78" s="102"/>
+      <c r="A78" s="94"/>
+      <c r="B78" s="99"/>
       <c r="C78" s="75"/>
       <c r="D78" s="83"/>
       <c r="E78" s="84"/>
@@ -5926,13 +5920,13 @@
       <c r="K78" s="87"/>
       <c r="L78" s="88"/>
       <c r="M78" s="89"/>
-      <c r="N78" s="93"/>
-      <c r="O78" s="91"/>
+      <c r="N78" s="91"/>
+      <c r="O78" s="90"/>
       <c r="Q78" s="19"/>
     </row>
     <row r="79" spans="1:17" ht="15.6">
-      <c r="A79" s="97"/>
-      <c r="B79" s="102"/>
+      <c r="A79" s="94"/>
+      <c r="B79" s="99"/>
       <c r="C79" s="75"/>
       <c r="D79" s="83"/>
       <c r="E79" s="84"/>
@@ -5944,13 +5938,13 @@
       <c r="K79" s="87"/>
       <c r="L79" s="88"/>
       <c r="M79" s="89"/>
-      <c r="N79" s="93"/>
-      <c r="O79" s="91"/>
+      <c r="N79" s="91"/>
+      <c r="O79" s="90"/>
       <c r="Q79" s="19"/>
     </row>
     <row r="80" spans="1:17" ht="15.6">
-      <c r="A80" s="97"/>
-      <c r="B80" s="102"/>
+      <c r="A80" s="94"/>
+      <c r="B80" s="99"/>
       <c r="C80" s="82"/>
       <c r="D80" s="83"/>
       <c r="E80" s="84"/>
@@ -5962,13 +5956,13 @@
       <c r="K80" s="87"/>
       <c r="L80" s="88"/>
       <c r="M80" s="89"/>
-      <c r="N80" s="93"/>
-      <c r="O80" s="91"/>
+      <c r="N80" s="91"/>
+      <c r="O80" s="90"/>
       <c r="Q80" s="19"/>
     </row>
     <row r="81" spans="1:17" ht="15.6">
-      <c r="A81" s="97"/>
-      <c r="B81" s="102"/>
+      <c r="A81" s="94"/>
+      <c r="B81" s="99"/>
       <c r="C81" s="82"/>
       <c r="D81" s="83"/>
       <c r="E81" s="84"/>
@@ -5980,13 +5974,13 @@
       <c r="K81" s="87"/>
       <c r="L81" s="88"/>
       <c r="M81" s="89"/>
-      <c r="N81" s="93"/>
-      <c r="O81" s="91"/>
+      <c r="N81" s="91"/>
+      <c r="O81" s="90"/>
       <c r="Q81" s="19"/>
     </row>
     <row r="82" spans="1:17" ht="15.6">
-      <c r="A82" s="97"/>
-      <c r="B82" s="102"/>
+      <c r="A82" s="94"/>
+      <c r="B82" s="99"/>
       <c r="C82" s="82"/>
       <c r="D82" s="83"/>
       <c r="E82" s="84"/>
@@ -5998,13 +5992,13 @@
       <c r="K82" s="87"/>
       <c r="L82" s="88"/>
       <c r="M82" s="89"/>
-      <c r="N82" s="93"/>
-      <c r="O82" s="91"/>
+      <c r="N82" s="91"/>
+      <c r="O82" s="90"/>
       <c r="Q82" s="19"/>
     </row>
     <row r="83" spans="1:17" ht="15.6">
-      <c r="A83" s="97"/>
-      <c r="B83" s="102"/>
+      <c r="A83" s="94"/>
+      <c r="B83" s="99"/>
       <c r="C83" s="82"/>
       <c r="D83" s="83"/>
       <c r="E83" s="84"/>
@@ -6019,13 +6013,13 @@
         <v>0</v>
       </c>
       <c r="M83" s="89"/>
-      <c r="N83" s="93"/>
-      <c r="O83" s="91"/>
+      <c r="N83" s="91"/>
+      <c r="O83" s="90"/>
       <c r="Q83" s="19"/>
     </row>
     <row r="84" spans="1:17" ht="15.6">
-      <c r="A84" s="97"/>
-      <c r="B84" s="102"/>
+      <c r="A84" s="94"/>
+      <c r="B84" s="99"/>
       <c r="C84" s="82"/>
       <c r="D84" s="83"/>
       <c r="E84" s="84"/>
@@ -6034,16 +6028,16 @@
       <c r="H84" s="14"/>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
-      <c r="K84" s="106"/>
+      <c r="K84" s="103"/>
       <c r="L84" s="88"/>
       <c r="M84" s="89"/>
-      <c r="N84" s="93"/>
-      <c r="O84" s="91"/>
+      <c r="N84" s="91"/>
+      <c r="O84" s="90"/>
       <c r="Q84" s="19"/>
     </row>
     <row r="85" spans="1:17" ht="15.6">
-      <c r="A85" s="97"/>
-      <c r="B85" s="102"/>
+      <c r="A85" s="94"/>
+      <c r="B85" s="99"/>
       <c r="C85" s="82"/>
       <c r="D85" s="83"/>
       <c r="E85" s="84"/>
@@ -6055,13 +6049,13 @@
       <c r="K85" s="87"/>
       <c r="L85" s="88"/>
       <c r="M85" s="89"/>
-      <c r="N85" s="93"/>
-      <c r="O85" s="91"/>
+      <c r="N85" s="91"/>
+      <c r="O85" s="90"/>
       <c r="Q85" s="19"/>
     </row>
     <row r="86" spans="1:17" ht="15.6">
-      <c r="A86" s="97"/>
-      <c r="B86" s="102"/>
+      <c r="A86" s="94"/>
+      <c r="B86" s="99"/>
       <c r="C86" s="82"/>
       <c r="D86" s="83"/>
       <c r="E86" s="84"/>
@@ -6070,16 +6064,16 @@
       <c r="H86" s="14"/>
       <c r="I86" s="14"/>
       <c r="J86" s="14"/>
-      <c r="K86" s="100"/>
+      <c r="K86" s="97"/>
       <c r="L86" s="88"/>
       <c r="M86" s="89"/>
-      <c r="N86" s="93"/>
-      <c r="O86" s="91"/>
+      <c r="N86" s="91"/>
+      <c r="O86" s="90"/>
       <c r="Q86" s="19"/>
     </row>
     <row r="87" spans="1:17" ht="15.6">
-      <c r="A87" s="97"/>
-      <c r="B87" s="102"/>
+      <c r="A87" s="94"/>
+      <c r="B87" s="99"/>
       <c r="C87" s="82"/>
       <c r="D87" s="83"/>
       <c r="E87" s="84"/>
@@ -6091,13 +6085,13 @@
       <c r="K87" s="87"/>
       <c r="L87" s="88"/>
       <c r="M87" s="89"/>
-      <c r="N87" s="93"/>
-      <c r="O87" s="91"/>
+      <c r="N87" s="91"/>
+      <c r="O87" s="90"/>
       <c r="Q87" s="19"/>
     </row>
     <row r="88" spans="1:17" ht="15.6">
-      <c r="A88" s="97"/>
-      <c r="B88" s="102"/>
+      <c r="A88" s="94"/>
+      <c r="B88" s="99"/>
       <c r="C88" s="82"/>
       <c r="D88" s="83"/>
       <c r="E88" s="84"/>
@@ -6109,13 +6103,13 @@
       <c r="K88" s="87"/>
       <c r="L88" s="88"/>
       <c r="M88" s="89"/>
-      <c r="N88" s="93"/>
-      <c r="O88" s="91"/>
+      <c r="N88" s="91"/>
+      <c r="O88" s="90"/>
       <c r="Q88" s="19"/>
     </row>
     <row r="89" spans="1:17" ht="15.6">
-      <c r="A89" s="97"/>
-      <c r="B89" s="102"/>
+      <c r="A89" s="94"/>
+      <c r="B89" s="99"/>
       <c r="C89" s="82"/>
       <c r="D89" s="83"/>
       <c r="E89" s="84"/>
@@ -6127,13 +6121,13 @@
       <c r="K89" s="87"/>
       <c r="L89" s="88"/>
       <c r="M89" s="89"/>
-      <c r="N89" s="93"/>
-      <c r="O89" s="91"/>
+      <c r="N89" s="91"/>
+      <c r="O89" s="90"/>
       <c r="Q89" s="19"/>
     </row>
     <row r="90" spans="1:17" ht="15.6">
-      <c r="A90" s="97"/>
-      <c r="B90" s="102"/>
+      <c r="A90" s="94"/>
+      <c r="B90" s="99"/>
       <c r="C90" s="82"/>
       <c r="D90" s="83"/>
       <c r="E90" s="84"/>
@@ -6148,13 +6142,13 @@
         <v>0</v>
       </c>
       <c r="M90" s="89"/>
-      <c r="N90" s="93"/>
-      <c r="O90" s="91"/>
+      <c r="N90" s="91"/>
+      <c r="O90" s="90"/>
       <c r="Q90" s="19"/>
     </row>
     <row r="91" spans="1:17" ht="15.6">
-      <c r="A91" s="97"/>
-      <c r="B91" s="102"/>
+      <c r="A91" s="94"/>
+      <c r="B91" s="99"/>
       <c r="C91" s="82"/>
       <c r="D91" s="83"/>
       <c r="E91" s="84"/>
@@ -6166,1098 +6160,1098 @@
       <c r="K91" s="87"/>
       <c r="L91" s="88"/>
       <c r="M91" s="89"/>
-      <c r="N91" s="93"/>
-      <c r="O91" s="91"/>
+      <c r="N91" s="91"/>
+      <c r="O91" s="90"/>
       <c r="Q91" s="19"/>
     </row>
     <row r="92" spans="1:17" ht="15.6">
-      <c r="A92" s="107"/>
-      <c r="B92" s="102"/>
+      <c r="A92" s="104"/>
+      <c r="B92" s="99"/>
       <c r="C92" s="75"/>
       <c r="D92" s="43"/>
       <c r="E92" s="30"/>
-      <c r="F92" s="108"/>
-      <c r="G92" s="109"/>
+      <c r="F92" s="105"/>
+      <c r="G92" s="106"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
-      <c r="K92" s="110"/>
+      <c r="K92" s="107"/>
       <c r="L92" s="36"/>
-      <c r="M92" s="111"/>
+      <c r="M92" s="108"/>
       <c r="N92" s="37"/>
-      <c r="O92" s="91"/>
+      <c r="O92" s="90"/>
       <c r="Q92" s="19"/>
     </row>
     <row r="93" spans="1:17" ht="15.6">
-      <c r="A93" s="107"/>
-      <c r="B93" s="102"/>
+      <c r="A93" s="104"/>
+      <c r="B93" s="99"/>
       <c r="C93" s="75"/>
       <c r="D93" s="43"/>
       <c r="E93" s="30"/>
-      <c r="F93" s="108"/>
-      <c r="G93" s="109"/>
+      <c r="F93" s="105"/>
+      <c r="G93" s="106"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
-      <c r="K93" s="110"/>
+      <c r="K93" s="107"/>
       <c r="L93" s="36"/>
-      <c r="M93" s="111"/>
+      <c r="M93" s="108"/>
       <c r="N93" s="37"/>
-      <c r="O93" s="91"/>
+      <c r="O93" s="90"/>
       <c r="Q93" s="19"/>
     </row>
     <row r="94" spans="1:17" ht="15.6">
-      <c r="A94" s="107"/>
-      <c r="B94" s="102"/>
+      <c r="A94" s="104"/>
+      <c r="B94" s="99"/>
       <c r="C94" s="75"/>
       <c r="D94" s="43"/>
       <c r="E94" s="30"/>
-      <c r="F94" s="108"/>
-      <c r="G94" s="109"/>
+      <c r="F94" s="105"/>
+      <c r="G94" s="106"/>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
-      <c r="K94" s="110"/>
+      <c r="K94" s="107"/>
       <c r="L94" s="36"/>
-      <c r="M94" s="111"/>
+      <c r="M94" s="108"/>
       <c r="N94" s="37"/>
-      <c r="O94" s="91"/>
+      <c r="O94" s="90"/>
       <c r="Q94" s="19"/>
     </row>
     <row r="95" spans="1:17" ht="15.6">
-      <c r="A95" s="107"/>
-      <c r="B95" s="102"/>
+      <c r="A95" s="104"/>
+      <c r="B95" s="99"/>
       <c r="C95" s="75"/>
       <c r="D95" s="43"/>
       <c r="E95" s="30"/>
-      <c r="F95" s="108"/>
-      <c r="G95" s="109"/>
+      <c r="F95" s="105"/>
+      <c r="G95" s="106"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
-      <c r="K95" s="110"/>
+      <c r="K95" s="107"/>
       <c r="L95" s="36"/>
-      <c r="M95" s="111"/>
+      <c r="M95" s="108"/>
       <c r="N95" s="37"/>
-      <c r="O95" s="91"/>
+      <c r="O95" s="90"/>
       <c r="Q95" s="19"/>
     </row>
     <row r="96" spans="1:17" ht="15.6">
-      <c r="A96" s="107"/>
-      <c r="B96" s="102"/>
+      <c r="A96" s="104"/>
+      <c r="B96" s="99"/>
       <c r="C96" s="75"/>
       <c r="D96" s="43"/>
       <c r="E96" s="30"/>
-      <c r="F96" s="108"/>
-      <c r="G96" s="109"/>
+      <c r="F96" s="105"/>
+      <c r="G96" s="106"/>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
-      <c r="K96" s="110"/>
+      <c r="K96" s="107"/>
       <c r="L96" s="36"/>
-      <c r="M96" s="111"/>
+      <c r="M96" s="108"/>
       <c r="N96" s="37"/>
-      <c r="O96" s="91"/>
+      <c r="O96" s="90"/>
       <c r="Q96" s="19"/>
     </row>
     <row r="97" spans="1:17" ht="15.6">
-      <c r="A97" s="107"/>
-      <c r="B97" s="102"/>
+      <c r="A97" s="104"/>
+      <c r="B97" s="99"/>
       <c r="C97" s="82"/>
       <c r="D97" s="43"/>
       <c r="E97" s="30"/>
-      <c r="F97" s="108"/>
-      <c r="G97" s="109"/>
+      <c r="F97" s="105"/>
+      <c r="G97" s="106"/>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
-      <c r="K97" s="110"/>
+      <c r="K97" s="107"/>
       <c r="L97" s="36"/>
-      <c r="M97" s="111"/>
+      <c r="M97" s="108"/>
       <c r="N97" s="37"/>
-      <c r="O97" s="91"/>
+      <c r="O97" s="90"/>
       <c r="Q97" s="19"/>
     </row>
     <row r="98" spans="1:17" ht="15.6">
-      <c r="A98" s="107"/>
-      <c r="B98" s="102"/>
+      <c r="A98" s="104"/>
+      <c r="B98" s="99"/>
       <c r="C98" s="75"/>
       <c r="D98" s="43"/>
       <c r="E98" s="30"/>
-      <c r="F98" s="108"/>
-      <c r="G98" s="109"/>
+      <c r="F98" s="105"/>
+      <c r="G98" s="106"/>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
-      <c r="K98" s="110"/>
+      <c r="K98" s="107"/>
       <c r="L98" s="36"/>
-      <c r="M98" s="111"/>
+      <c r="M98" s="108"/>
       <c r="N98" s="37"/>
-      <c r="O98" s="91"/>
+      <c r="O98" s="90"/>
       <c r="Q98" s="19"/>
     </row>
     <row r="99" spans="1:17" ht="15.6">
-      <c r="A99" s="107"/>
-      <c r="B99" s="102"/>
+      <c r="A99" s="104"/>
+      <c r="B99" s="99"/>
       <c r="C99" s="75"/>
       <c r="D99" s="43"/>
       <c r="E99" s="30"/>
-      <c r="F99" s="108"/>
-      <c r="G99" s="109"/>
+      <c r="F99" s="105"/>
+      <c r="G99" s="106"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="110"/>
+      <c r="K99" s="107"/>
       <c r="L99" s="36"/>
-      <c r="M99" s="111"/>
+      <c r="M99" s="108"/>
       <c r="N99" s="37"/>
-      <c r="O99" s="91"/>
+      <c r="O99" s="90"/>
       <c r="Q99" s="19"/>
     </row>
     <row r="100" spans="1:17" ht="15.6">
-      <c r="A100" s="107"/>
-      <c r="B100" s="102"/>
+      <c r="A100" s="104"/>
+      <c r="B100" s="99"/>
       <c r="C100" s="75"/>
       <c r="D100" s="43"/>
       <c r="E100" s="30"/>
-      <c r="F100" s="108"/>
-      <c r="G100" s="109"/>
+      <c r="F100" s="105"/>
+      <c r="G100" s="106"/>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
-      <c r="K100" s="110"/>
+      <c r="K100" s="107"/>
       <c r="L100" s="36"/>
-      <c r="M100" s="111"/>
+      <c r="M100" s="108"/>
       <c r="N100" s="37"/>
-      <c r="O100" s="91"/>
+      <c r="O100" s="90"/>
       <c r="Q100" s="19"/>
     </row>
     <row r="101" spans="1:17" ht="15.6">
-      <c r="A101" s="107"/>
-      <c r="B101" s="102"/>
+      <c r="A101" s="104"/>
+      <c r="B101" s="99"/>
       <c r="C101" s="75"/>
       <c r="D101" s="43"/>
       <c r="E101" s="30"/>
-      <c r="F101" s="108"/>
-      <c r="G101" s="109"/>
+      <c r="F101" s="105"/>
+      <c r="G101" s="106"/>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
-      <c r="K101" s="110"/>
+      <c r="K101" s="107"/>
       <c r="L101" s="36"/>
-      <c r="M101" s="111"/>
+      <c r="M101" s="108"/>
       <c r="N101" s="37"/>
-      <c r="O101" s="91"/>
+      <c r="O101" s="90"/>
       <c r="Q101" s="19"/>
     </row>
     <row r="102" spans="1:17" ht="15.6">
-      <c r="A102" s="107"/>
-      <c r="B102" s="102"/>
+      <c r="A102" s="104"/>
+      <c r="B102" s="99"/>
       <c r="C102" s="75"/>
       <c r="D102" s="43"/>
       <c r="E102" s="30"/>
-      <c r="F102" s="108"/>
-      <c r="G102" s="109"/>
+      <c r="F102" s="105"/>
+      <c r="G102" s="106"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
-      <c r="K102" s="110"/>
+      <c r="K102" s="107"/>
       <c r="L102" s="36"/>
-      <c r="M102" s="111"/>
+      <c r="M102" s="108"/>
       <c r="N102" s="37"/>
-      <c r="O102" s="91"/>
+      <c r="O102" s="90"/>
       <c r="Q102" s="19"/>
     </row>
     <row r="103" spans="1:17" ht="15.6">
-      <c r="A103" s="107"/>
-      <c r="B103" s="102"/>
+      <c r="A103" s="104"/>
+      <c r="B103" s="99"/>
       <c r="C103" s="75"/>
       <c r="D103" s="43"/>
       <c r="E103" s="30"/>
-      <c r="F103" s="108"/>
-      <c r="G103" s="109"/>
+      <c r="F103" s="105"/>
+      <c r="G103" s="106"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
-      <c r="K103" s="110"/>
+      <c r="K103" s="107"/>
       <c r="L103" s="88">
         <f ca="1">SUMIF($K$8:$K229,"4",$H$8:$H$151)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="111"/>
+      <c r="M103" s="108"/>
       <c r="N103" s="37"/>
-      <c r="O103" s="91"/>
+      <c r="O103" s="90"/>
       <c r="Q103" s="19"/>
     </row>
     <row r="104" spans="1:17" ht="15.6">
-      <c r="A104" s="107"/>
-      <c r="B104" s="102"/>
+      <c r="A104" s="104"/>
+      <c r="B104" s="99"/>
       <c r="C104" s="75"/>
       <c r="D104" s="43"/>
       <c r="E104" s="30"/>
-      <c r="F104" s="108"/>
-      <c r="G104" s="109"/>
+      <c r="F104" s="105"/>
+      <c r="G104" s="106"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
-      <c r="K104" s="110"/>
+      <c r="K104" s="107"/>
       <c r="L104" s="36"/>
-      <c r="M104" s="111"/>
+      <c r="M104" s="108"/>
       <c r="N104" s="37"/>
-      <c r="O104" s="91"/>
+      <c r="O104" s="90"/>
       <c r="Q104" s="19"/>
     </row>
     <row r="105" spans="1:17" ht="15.6">
-      <c r="A105" s="107"/>
-      <c r="B105" s="102"/>
+      <c r="A105" s="104"/>
+      <c r="B105" s="99"/>
       <c r="C105" s="75"/>
       <c r="D105" s="43"/>
       <c r="E105" s="30"/>
-      <c r="F105" s="108"/>
-      <c r="G105" s="109"/>
+      <c r="F105" s="105"/>
+      <c r="G105" s="106"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
-      <c r="K105" s="110"/>
+      <c r="K105" s="107"/>
       <c r="L105" s="36"/>
-      <c r="M105" s="111"/>
+      <c r="M105" s="108"/>
       <c r="N105" s="37"/>
-      <c r="O105" s="91"/>
+      <c r="O105" s="90"/>
       <c r="Q105" s="19"/>
     </row>
     <row r="106" spans="1:17" ht="15.6">
-      <c r="A106" s="107"/>
-      <c r="B106" s="102"/>
+      <c r="A106" s="104"/>
+      <c r="B106" s="99"/>
       <c r="C106" s="75"/>
       <c r="D106" s="43"/>
       <c r="E106" s="30"/>
-      <c r="F106" s="108"/>
-      <c r="G106" s="109"/>
+      <c r="F106" s="105"/>
+      <c r="G106" s="106"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
-      <c r="K106" s="110"/>
+      <c r="K106" s="107"/>
       <c r="L106" s="36"/>
-      <c r="M106" s="111"/>
-      <c r="N106" s="98"/>
-      <c r="O106" s="91"/>
+      <c r="M106" s="108"/>
+      <c r="N106" s="95"/>
+      <c r="O106" s="90"/>
       <c r="Q106" s="19"/>
     </row>
     <row r="107" spans="1:17" ht="15.6">
-      <c r="A107" s="107"/>
-      <c r="B107" s="102"/>
+      <c r="A107" s="104"/>
+      <c r="B107" s="99"/>
       <c r="C107" s="75"/>
       <c r="D107" s="43"/>
       <c r="E107" s="30"/>
-      <c r="F107" s="108"/>
-      <c r="G107" s="109"/>
+      <c r="F107" s="105"/>
+      <c r="G107" s="106"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
-      <c r="K107" s="110"/>
+      <c r="K107" s="107"/>
       <c r="L107" s="36"/>
-      <c r="M107" s="111"/>
-      <c r="N107" s="112"/>
-      <c r="O107" s="91"/>
+      <c r="M107" s="108"/>
+      <c r="N107" s="109"/>
+      <c r="O107" s="90"/>
       <c r="Q107" s="19"/>
     </row>
     <row r="108" spans="1:17" ht="15.6">
-      <c r="A108" s="107"/>
-      <c r="B108" s="102"/>
+      <c r="A108" s="104"/>
+      <c r="B108" s="99"/>
       <c r="C108" s="75"/>
       <c r="D108" s="43"/>
       <c r="E108" s="30"/>
-      <c r="F108" s="108"/>
-      <c r="G108" s="109"/>
+      <c r="F108" s="105"/>
+      <c r="G108" s="106"/>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
-      <c r="K108" s="110"/>
+      <c r="K108" s="107"/>
       <c r="L108" s="36"/>
-      <c r="M108" s="111"/>
-      <c r="N108" s="112"/>
-      <c r="O108" s="91"/>
+      <c r="M108" s="108"/>
+      <c r="N108" s="109"/>
+      <c r="O108" s="90"/>
       <c r="Q108" s="19"/>
     </row>
     <row r="109" spans="1:17" ht="15.6">
-      <c r="A109" s="107"/>
-      <c r="B109" s="102"/>
+      <c r="A109" s="104"/>
+      <c r="B109" s="99"/>
       <c r="C109" s="75"/>
       <c r="D109" s="43"/>
       <c r="E109" s="30"/>
-      <c r="F109" s="108"/>
-      <c r="G109" s="109"/>
+      <c r="F109" s="105"/>
+      <c r="G109" s="106"/>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
-      <c r="K109" s="110"/>
+      <c r="K109" s="107"/>
       <c r="L109" s="36"/>
-      <c r="M109" s="111"/>
-      <c r="N109" s="112"/>
-      <c r="O109" s="91"/>
+      <c r="M109" s="108"/>
+      <c r="N109" s="109"/>
+      <c r="O109" s="90"/>
       <c r="Q109" s="19"/>
     </row>
     <row r="110" spans="1:17" ht="15.6">
-      <c r="A110" s="107"/>
-      <c r="B110" s="102"/>
+      <c r="A110" s="104"/>
+      <c r="B110" s="99"/>
       <c r="C110" s="75"/>
       <c r="D110" s="43"/>
       <c r="E110" s="30"/>
-      <c r="F110" s="108"/>
-      <c r="G110" s="109"/>
+      <c r="F110" s="105"/>
+      <c r="G110" s="106"/>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
-      <c r="K110" s="110"/>
+      <c r="K110" s="107"/>
       <c r="L110" s="36"/>
-      <c r="M110" s="111"/>
-      <c r="N110" s="112"/>
-      <c r="O110" s="91"/>
+      <c r="M110" s="108"/>
+      <c r="N110" s="109"/>
+      <c r="O110" s="90"/>
       <c r="Q110" s="19"/>
     </row>
     <row r="111" spans="1:17" ht="15.6">
-      <c r="A111" s="107"/>
-      <c r="B111" s="102"/>
+      <c r="A111" s="104"/>
+      <c r="B111" s="99"/>
       <c r="C111" s="75"/>
       <c r="D111" s="43"/>
       <c r="E111" s="30"/>
-      <c r="F111" s="108"/>
-      <c r="G111" s="109"/>
+      <c r="F111" s="105"/>
+      <c r="G111" s="106"/>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
-      <c r="K111" s="110"/>
+      <c r="K111" s="107"/>
       <c r="L111" s="36"/>
-      <c r="M111" s="111"/>
-      <c r="N111" s="112"/>
-      <c r="O111" s="91"/>
+      <c r="M111" s="108"/>
+      <c r="N111" s="109"/>
+      <c r="O111" s="90"/>
       <c r="Q111" s="19"/>
     </row>
     <row r="112" spans="1:17" ht="15.6">
-      <c r="A112" s="107"/>
-      <c r="B112" s="102"/>
+      <c r="A112" s="104"/>
+      <c r="B112" s="99"/>
       <c r="C112" s="75"/>
       <c r="D112" s="43"/>
       <c r="E112" s="30"/>
-      <c r="F112" s="108"/>
-      <c r="G112" s="109"/>
+      <c r="F112" s="105"/>
+      <c r="G112" s="106"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
-      <c r="K112" s="110"/>
+      <c r="K112" s="107"/>
       <c r="L112" s="36"/>
-      <c r="M112" s="111"/>
-      <c r="N112" s="112"/>
-      <c r="O112" s="91"/>
+      <c r="M112" s="108"/>
+      <c r="N112" s="109"/>
+      <c r="O112" s="90"/>
       <c r="Q112" s="19"/>
     </row>
     <row r="113" spans="1:17" ht="15.6">
-      <c r="A113" s="107"/>
-      <c r="B113" s="102"/>
+      <c r="A113" s="104"/>
+      <c r="B113" s="99"/>
       <c r="C113" s="75"/>
       <c r="D113" s="43"/>
       <c r="E113" s="30"/>
-      <c r="F113" s="108"/>
-      <c r="G113" s="109"/>
+      <c r="F113" s="105"/>
+      <c r="G113" s="106"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
-      <c r="K113" s="110"/>
+      <c r="K113" s="107"/>
       <c r="L113" s="36"/>
-      <c r="M113" s="111"/>
-      <c r="N113" s="112"/>
-      <c r="O113" s="91"/>
+      <c r="M113" s="108"/>
+      <c r="N113" s="109"/>
+      <c r="O113" s="90"/>
       <c r="Q113" s="19"/>
     </row>
     <row r="114" spans="1:17" ht="15.6">
-      <c r="A114" s="107"/>
-      <c r="B114" s="102"/>
+      <c r="A114" s="104"/>
+      <c r="B114" s="99"/>
       <c r="C114" s="75"/>
       <c r="D114" s="43"/>
       <c r="E114" s="30"/>
-      <c r="F114" s="108"/>
-      <c r="G114" s="109"/>
+      <c r="F114" s="105"/>
+      <c r="G114" s="106"/>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
-      <c r="K114" s="110"/>
+      <c r="K114" s="107"/>
       <c r="L114" s="36"/>
-      <c r="M114" s="111"/>
-      <c r="N114" s="112"/>
-      <c r="O114" s="91"/>
+      <c r="M114" s="108"/>
+      <c r="N114" s="109"/>
+      <c r="O114" s="90"/>
       <c r="Q114" s="19"/>
     </row>
     <row r="115" spans="1:17" ht="15.6">
-      <c r="A115" s="107"/>
-      <c r="B115" s="102"/>
+      <c r="A115" s="104"/>
+      <c r="B115" s="99"/>
       <c r="C115" s="75"/>
       <c r="D115" s="43"/>
       <c r="E115" s="30"/>
-      <c r="F115" s="108"/>
-      <c r="G115" s="109"/>
+      <c r="F115" s="105"/>
+      <c r="G115" s="106"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
-      <c r="K115" s="110"/>
+      <c r="K115" s="107"/>
       <c r="L115" s="88"/>
-      <c r="M115" s="111"/>
-      <c r="N115" s="112"/>
-      <c r="O115" s="91"/>
+      <c r="M115" s="108"/>
+      <c r="N115" s="109"/>
+      <c r="O115" s="90"/>
       <c r="Q115" s="19"/>
     </row>
     <row r="116" spans="1:17" ht="15.6">
-      <c r="A116" s="107"/>
-      <c r="B116" s="102"/>
+      <c r="A116" s="104"/>
+      <c r="B116" s="99"/>
       <c r="C116" s="75"/>
       <c r="D116" s="43"/>
       <c r="E116" s="30"/>
-      <c r="F116" s="108"/>
-      <c r="G116" s="109"/>
+      <c r="F116" s="105"/>
+      <c r="G116" s="106"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
-      <c r="K116" s="110"/>
+      <c r="K116" s="107"/>
       <c r="L116" s="36"/>
-      <c r="M116" s="111"/>
-      <c r="N116" s="112"/>
-      <c r="O116" s="91"/>
+      <c r="M116" s="108"/>
+      <c r="N116" s="109"/>
+      <c r="O116" s="90"/>
       <c r="Q116" s="19"/>
     </row>
     <row r="117" spans="1:17" ht="15.6">
-      <c r="A117" s="107"/>
-      <c r="B117" s="102"/>
+      <c r="A117" s="104"/>
+      <c r="B117" s="99"/>
       <c r="C117" s="75"/>
       <c r="D117" s="43"/>
       <c r="E117" s="30"/>
-      <c r="F117" s="108"/>
-      <c r="G117" s="109"/>
+      <c r="F117" s="105"/>
+      <c r="G117" s="106"/>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
-      <c r="K117" s="110"/>
+      <c r="K117" s="107"/>
       <c r="L117" s="36"/>
-      <c r="M117" s="111"/>
-      <c r="N117" s="112"/>
-      <c r="O117" s="91"/>
+      <c r="M117" s="108"/>
+      <c r="N117" s="109"/>
+      <c r="O117" s="90"/>
       <c r="Q117" s="19"/>
     </row>
     <row r="118" spans="1:17" ht="15.6">
-      <c r="A118" s="107"/>
-      <c r="B118" s="102"/>
+      <c r="A118" s="104"/>
+      <c r="B118" s="99"/>
       <c r="C118" s="75"/>
       <c r="D118" s="43"/>
       <c r="E118" s="30"/>
-      <c r="F118" s="108"/>
-      <c r="G118" s="109"/>
+      <c r="F118" s="105"/>
+      <c r="G118" s="106"/>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
-      <c r="K118" s="110"/>
+      <c r="K118" s="107"/>
       <c r="L118" s="36"/>
-      <c r="M118" s="111"/>
-      <c r="N118" s="112"/>
-      <c r="O118" s="91"/>
+      <c r="M118" s="108"/>
+      <c r="N118" s="109"/>
+      <c r="O118" s="90"/>
       <c r="Q118" s="19"/>
     </row>
     <row r="119" spans="1:17" ht="15.6">
-      <c r="A119" s="107"/>
-      <c r="B119" s="102"/>
+      <c r="A119" s="104"/>
+      <c r="B119" s="99"/>
       <c r="C119" s="75"/>
       <c r="D119" s="43"/>
       <c r="E119" s="30"/>
-      <c r="F119" s="108"/>
-      <c r="G119" s="109"/>
+      <c r="F119" s="105"/>
+      <c r="G119" s="106"/>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
-      <c r="K119" s="110"/>
+      <c r="K119" s="107"/>
       <c r="L119" s="36"/>
-      <c r="M119" s="111"/>
-      <c r="N119" s="112"/>
-      <c r="O119" s="91"/>
+      <c r="M119" s="108"/>
+      <c r="N119" s="109"/>
+      <c r="O119" s="90"/>
       <c r="Q119" s="19"/>
     </row>
     <row r="120" spans="1:17" ht="15.6">
-      <c r="A120" s="107"/>
-      <c r="B120" s="102"/>
+      <c r="A120" s="104"/>
+      <c r="B120" s="99"/>
       <c r="C120" s="75"/>
       <c r="D120" s="43"/>
       <c r="E120" s="30"/>
-      <c r="F120" s="108"/>
-      <c r="G120" s="109"/>
+      <c r="F120" s="105"/>
+      <c r="G120" s="106"/>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
-      <c r="K120" s="110"/>
+      <c r="K120" s="107"/>
       <c r="L120" s="36"/>
-      <c r="M120" s="111"/>
-      <c r="N120" s="112"/>
-      <c r="O120" s="91"/>
+      <c r="M120" s="108"/>
+      <c r="N120" s="109"/>
+      <c r="O120" s="90"/>
       <c r="Q120" s="19"/>
     </row>
     <row r="121" spans="1:17" ht="15.6">
-      <c r="A121" s="107"/>
-      <c r="B121" s="102"/>
+      <c r="A121" s="104"/>
+      <c r="B121" s="99"/>
       <c r="C121" s="75"/>
       <c r="D121" s="43"/>
       <c r="E121" s="30"/>
-      <c r="F121" s="108"/>
-      <c r="G121" s="109"/>
+      <c r="F121" s="105"/>
+      <c r="G121" s="106"/>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
-      <c r="K121" s="110"/>
+      <c r="K121" s="107"/>
       <c r="L121" s="36"/>
-      <c r="M121" s="111"/>
-      <c r="N121" s="112"/>
-      <c r="O121" s="91"/>
+      <c r="M121" s="108"/>
+      <c r="N121" s="109"/>
+      <c r="O121" s="90"/>
       <c r="Q121" s="19"/>
     </row>
     <row r="122" spans="1:17" ht="15.6">
-      <c r="A122" s="107"/>
-      <c r="B122" s="102"/>
+      <c r="A122" s="104"/>
+      <c r="B122" s="99"/>
       <c r="C122" s="75"/>
       <c r="D122" s="43"/>
       <c r="E122" s="30"/>
-      <c r="F122" s="108"/>
-      <c r="G122" s="109"/>
+      <c r="F122" s="105"/>
+      <c r="G122" s="106"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
-      <c r="K122" s="110"/>
+      <c r="K122" s="107"/>
       <c r="L122" s="36"/>
-      <c r="M122" s="111"/>
-      <c r="N122" s="112"/>
-      <c r="O122" s="91"/>
+      <c r="M122" s="108"/>
+      <c r="N122" s="109"/>
+      <c r="O122" s="90"/>
       <c r="Q122" s="19"/>
     </row>
     <row r="123" spans="1:17" ht="15.6">
-      <c r="A123" s="107"/>
-      <c r="B123" s="102"/>
+      <c r="A123" s="104"/>
+      <c r="B123" s="99"/>
       <c r="C123" s="75"/>
       <c r="D123" s="43"/>
       <c r="E123" s="30"/>
-      <c r="F123" s="108"/>
-      <c r="G123" s="109"/>
+      <c r="F123" s="105"/>
+      <c r="G123" s="106"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
-      <c r="K123" s="110"/>
+      <c r="K123" s="107"/>
       <c r="L123" s="36"/>
-      <c r="M123" s="111"/>
-      <c r="N123" s="112"/>
-      <c r="O123" s="91"/>
+      <c r="M123" s="108"/>
+      <c r="N123" s="109"/>
+      <c r="O123" s="90"/>
       <c r="Q123" s="19"/>
     </row>
     <row r="124" spans="1:17" ht="15.6">
-      <c r="A124" s="107"/>
-      <c r="B124" s="102"/>
+      <c r="A124" s="104"/>
+      <c r="B124" s="99"/>
       <c r="C124" s="75"/>
       <c r="D124" s="43"/>
       <c r="E124" s="30"/>
-      <c r="F124" s="108"/>
-      <c r="G124" s="109"/>
+      <c r="F124" s="105"/>
+      <c r="G124" s="106"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
-      <c r="K124" s="110"/>
+      <c r="K124" s="107"/>
       <c r="L124" s="36"/>
-      <c r="M124" s="111"/>
-      <c r="N124" s="112"/>
-      <c r="O124" s="91"/>
+      <c r="M124" s="108"/>
+      <c r="N124" s="109"/>
+      <c r="O124" s="90"/>
       <c r="Q124" s="19"/>
     </row>
     <row r="125" spans="1:17" ht="15.6">
-      <c r="A125" s="107"/>
-      <c r="B125" s="102"/>
+      <c r="A125" s="104"/>
+      <c r="B125" s="99"/>
       <c r="C125" s="75"/>
       <c r="D125" s="43"/>
       <c r="E125" s="30"/>
-      <c r="F125" s="108"/>
-      <c r="G125" s="109"/>
+      <c r="F125" s="105"/>
+      <c r="G125" s="106"/>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
-      <c r="K125" s="110"/>
+      <c r="K125" s="107"/>
       <c r="L125" s="36"/>
-      <c r="M125" s="111"/>
-      <c r="N125" s="112"/>
-      <c r="O125" s="91"/>
+      <c r="M125" s="108"/>
+      <c r="N125" s="109"/>
+      <c r="O125" s="90"/>
       <c r="Q125" s="19"/>
     </row>
     <row r="126" spans="1:17" ht="15.6">
-      <c r="A126" s="107"/>
-      <c r="B126" s="102"/>
+      <c r="A126" s="104"/>
+      <c r="B126" s="99"/>
       <c r="C126" s="75"/>
       <c r="D126" s="43"/>
       <c r="E126" s="30"/>
-      <c r="F126" s="108"/>
-      <c r="G126" s="109"/>
+      <c r="F126" s="105"/>
+      <c r="G126" s="106"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
-      <c r="K126" s="110"/>
+      <c r="K126" s="107"/>
       <c r="L126" s="36"/>
-      <c r="M126" s="111"/>
-      <c r="N126" s="112"/>
-      <c r="O126" s="91"/>
+      <c r="M126" s="108"/>
+      <c r="N126" s="109"/>
+      <c r="O126" s="90"/>
       <c r="Q126" s="19"/>
     </row>
     <row r="127" spans="1:17" ht="15.6">
-      <c r="A127" s="107"/>
-      <c r="B127" s="102"/>
+      <c r="A127" s="104"/>
+      <c r="B127" s="99"/>
       <c r="C127" s="75"/>
       <c r="D127" s="43"/>
       <c r="E127" s="30"/>
-      <c r="F127" s="108"/>
-      <c r="G127" s="109"/>
+      <c r="F127" s="105"/>
+      <c r="G127" s="106"/>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
-      <c r="K127" s="110"/>
+      <c r="K127" s="107"/>
       <c r="L127" s="36"/>
-      <c r="M127" s="111"/>
-      <c r="N127" s="112"/>
-      <c r="O127" s="91"/>
+      <c r="M127" s="108"/>
+      <c r="N127" s="109"/>
+      <c r="O127" s="90"/>
       <c r="Q127" s="19"/>
     </row>
     <row r="128" spans="1:17" ht="15.6">
-      <c r="A128" s="107"/>
-      <c r="B128" s="102"/>
+      <c r="A128" s="104"/>
+      <c r="B128" s="99"/>
       <c r="C128" s="75"/>
       <c r="D128" s="43"/>
       <c r="E128" s="30"/>
-      <c r="F128" s="108"/>
-      <c r="G128" s="109"/>
+      <c r="F128" s="105"/>
+      <c r="G128" s="106"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
-      <c r="K128" s="110"/>
+      <c r="K128" s="107"/>
       <c r="L128" s="36"/>
-      <c r="M128" s="111"/>
-      <c r="N128" s="112"/>
-      <c r="O128" s="91"/>
+      <c r="M128" s="108"/>
+      <c r="N128" s="109"/>
+      <c r="O128" s="90"/>
       <c r="Q128" s="19"/>
     </row>
     <row r="129" spans="1:17" ht="15.6">
-      <c r="A129" s="107"/>
-      <c r="B129" s="102"/>
+      <c r="A129" s="104"/>
+      <c r="B129" s="99"/>
       <c r="C129" s="75"/>
       <c r="D129" s="43"/>
       <c r="E129" s="30"/>
-      <c r="F129" s="108"/>
-      <c r="G129" s="109"/>
+      <c r="F129" s="105"/>
+      <c r="G129" s="106"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
-      <c r="K129" s="110"/>
+      <c r="K129" s="107"/>
       <c r="L129" s="36"/>
-      <c r="M129" s="111"/>
-      <c r="N129" s="112"/>
-      <c r="O129" s="91"/>
+      <c r="M129" s="108"/>
+      <c r="N129" s="109"/>
+      <c r="O129" s="90"/>
       <c r="Q129" s="19"/>
     </row>
     <row r="130" spans="1:17" ht="15.6">
-      <c r="A130" s="107"/>
-      <c r="B130" s="102"/>
+      <c r="A130" s="104"/>
+      <c r="B130" s="99"/>
       <c r="C130" s="75"/>
       <c r="D130" s="43"/>
       <c r="E130" s="30"/>
-      <c r="F130" s="108"/>
-      <c r="G130" s="109"/>
+      <c r="F130" s="105"/>
+      <c r="G130" s="106"/>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
-      <c r="K130" s="110"/>
+      <c r="K130" s="107"/>
       <c r="L130" s="36"/>
-      <c r="M130" s="111"/>
-      <c r="N130" s="112"/>
-      <c r="O130" s="91"/>
+      <c r="M130" s="108"/>
+      <c r="N130" s="109"/>
+      <c r="O130" s="90"/>
       <c r="Q130" s="19"/>
     </row>
     <row r="131" spans="1:17" ht="15.6">
-      <c r="A131" s="107"/>
-      <c r="B131" s="102"/>
+      <c r="A131" s="104"/>
+      <c r="B131" s="99"/>
       <c r="C131" s="75"/>
       <c r="D131" s="43"/>
       <c r="E131" s="30"/>
-      <c r="F131" s="108"/>
-      <c r="G131" s="109"/>
+      <c r="F131" s="105"/>
+      <c r="G131" s="106"/>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
-      <c r="K131" s="110"/>
+      <c r="K131" s="107"/>
       <c r="L131" s="36"/>
-      <c r="M131" s="111"/>
-      <c r="N131" s="112"/>
-      <c r="O131" s="91"/>
+      <c r="M131" s="108"/>
+      <c r="N131" s="109"/>
+      <c r="O131" s="90"/>
       <c r="Q131" s="19"/>
     </row>
     <row r="132" spans="1:17" ht="15.6">
-      <c r="A132" s="107"/>
-      <c r="B132" s="102"/>
+      <c r="A132" s="104"/>
+      <c r="B132" s="99"/>
       <c r="C132" s="75"/>
       <c r="D132" s="43"/>
       <c r="E132" s="30"/>
-      <c r="F132" s="108"/>
-      <c r="G132" s="109"/>
+      <c r="F132" s="105"/>
+      <c r="G132" s="106"/>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
-      <c r="K132" s="110"/>
+      <c r="K132" s="107"/>
       <c r="L132" s="36"/>
-      <c r="M132" s="111"/>
-      <c r="N132" s="112"/>
-      <c r="O132" s="91"/>
+      <c r="M132" s="108"/>
+      <c r="N132" s="109"/>
+      <c r="O132" s="90"/>
       <c r="Q132" s="19"/>
     </row>
     <row r="133" spans="1:17" ht="15.6">
-      <c r="A133" s="107"/>
-      <c r="B133" s="102"/>
+      <c r="A133" s="104"/>
+      <c r="B133" s="99"/>
       <c r="C133" s="75"/>
       <c r="D133" s="43"/>
       <c r="E133" s="30"/>
-      <c r="F133" s="108"/>
-      <c r="G133" s="109"/>
+      <c r="F133" s="105"/>
+      <c r="G133" s="106"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
-      <c r="K133" s="110"/>
+      <c r="K133" s="107"/>
       <c r="L133" s="36"/>
-      <c r="M133" s="111"/>
-      <c r="N133" s="112"/>
-      <c r="O133" s="91"/>
+      <c r="M133" s="108"/>
+      <c r="N133" s="109"/>
+      <c r="O133" s="90"/>
       <c r="Q133" s="19"/>
     </row>
     <row r="134" spans="1:17" ht="15.6">
-      <c r="A134" s="107"/>
-      <c r="B134" s="102"/>
+      <c r="A134" s="104"/>
+      <c r="B134" s="99"/>
       <c r="C134" s="75"/>
       <c r="D134" s="43"/>
       <c r="E134" s="30"/>
-      <c r="F134" s="108"/>
-      <c r="G134" s="109"/>
+      <c r="F134" s="105"/>
+      <c r="G134" s="106"/>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
-      <c r="K134" s="110"/>
+      <c r="K134" s="107"/>
       <c r="L134" s="36"/>
-      <c r="M134" s="111"/>
-      <c r="N134" s="112"/>
-      <c r="O134" s="91"/>
+      <c r="M134" s="108"/>
+      <c r="N134" s="109"/>
+      <c r="O134" s="90"/>
       <c r="Q134" s="19"/>
     </row>
     <row r="135" spans="1:17" ht="15.6">
-      <c r="A135" s="107"/>
-      <c r="B135" s="102"/>
+      <c r="A135" s="104"/>
+      <c r="B135" s="99"/>
       <c r="C135" s="75"/>
       <c r="D135" s="43"/>
       <c r="E135" s="30"/>
-      <c r="F135" s="108"/>
-      <c r="G135" s="109"/>
+      <c r="F135" s="105"/>
+      <c r="G135" s="106"/>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
-      <c r="K135" s="110"/>
+      <c r="K135" s="107"/>
       <c r="L135" s="36"/>
-      <c r="M135" s="111"/>
-      <c r="N135" s="112"/>
-      <c r="O135" s="91"/>
+      <c r="M135" s="108"/>
+      <c r="N135" s="109"/>
+      <c r="O135" s="90"/>
       <c r="Q135" s="19"/>
     </row>
     <row r="136" spans="1:17" ht="15.6">
-      <c r="A136" s="107"/>
-      <c r="B136" s="102"/>
+      <c r="A136" s="104"/>
+      <c r="B136" s="99"/>
       <c r="C136" s="75"/>
       <c r="D136" s="43"/>
       <c r="E136" s="30"/>
-      <c r="F136" s="108"/>
-      <c r="G136" s="109"/>
+      <c r="F136" s="105"/>
+      <c r="G136" s="106"/>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
-      <c r="K136" s="110"/>
+      <c r="K136" s="107"/>
       <c r="L136" s="36"/>
-      <c r="M136" s="111"/>
-      <c r="N136" s="112"/>
-      <c r="O136" s="91"/>
+      <c r="M136" s="108"/>
+      <c r="N136" s="109"/>
+      <c r="O136" s="90"/>
       <c r="Q136" s="19"/>
     </row>
     <row r="137" spans="1:17" ht="15.6">
-      <c r="A137" s="107"/>
-      <c r="B137" s="102"/>
+      <c r="A137" s="104"/>
+      <c r="B137" s="99"/>
       <c r="C137" s="75"/>
       <c r="D137" s="43"/>
       <c r="E137" s="30"/>
-      <c r="F137" s="108"/>
-      <c r="G137" s="109"/>
+      <c r="F137" s="105"/>
+      <c r="G137" s="106"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
-      <c r="K137" s="110"/>
+      <c r="K137" s="107"/>
       <c r="L137" s="36"/>
-      <c r="M137" s="111"/>
-      <c r="N137" s="112"/>
-      <c r="O137" s="91"/>
+      <c r="M137" s="108"/>
+      <c r="N137" s="109"/>
+      <c r="O137" s="90"/>
       <c r="Q137" s="19"/>
     </row>
     <row r="138" spans="1:17" ht="15.6">
-      <c r="A138" s="107"/>
-      <c r="B138" s="102"/>
+      <c r="A138" s="104"/>
+      <c r="B138" s="99"/>
       <c r="C138" s="75"/>
       <c r="D138" s="43"/>
       <c r="E138" s="30"/>
-      <c r="F138" s="108"/>
-      <c r="G138" s="109"/>
+      <c r="F138" s="105"/>
+      <c r="G138" s="106"/>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
-      <c r="K138" s="110"/>
+      <c r="K138" s="107"/>
       <c r="L138" s="36"/>
-      <c r="M138" s="111"/>
-      <c r="N138" s="112"/>
-      <c r="O138" s="91"/>
+      <c r="M138" s="108"/>
+      <c r="N138" s="109"/>
+      <c r="O138" s="90"/>
       <c r="Q138" s="19"/>
     </row>
     <row r="139" spans="1:17" ht="15.6">
-      <c r="A139" s="107"/>
-      <c r="B139" s="102"/>
+      <c r="A139" s="104"/>
+      <c r="B139" s="99"/>
       <c r="C139" s="75"/>
       <c r="D139" s="43"/>
       <c r="E139" s="30"/>
-      <c r="F139" s="108"/>
-      <c r="G139" s="109"/>
+      <c r="F139" s="105"/>
+      <c r="G139" s="106"/>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
-      <c r="K139" s="110"/>
+      <c r="K139" s="107"/>
       <c r="L139" s="36"/>
-      <c r="M139" s="111"/>
-      <c r="N139" s="112"/>
-      <c r="O139" s="91"/>
+      <c r="M139" s="108"/>
+      <c r="N139" s="109"/>
+      <c r="O139" s="90"/>
       <c r="Q139" s="19"/>
     </row>
     <row r="140" spans="1:17" ht="15.6">
-      <c r="A140" s="107"/>
-      <c r="B140" s="102"/>
+      <c r="A140" s="104"/>
+      <c r="B140" s="99"/>
       <c r="C140" s="75"/>
       <c r="D140" s="43"/>
       <c r="E140" s="30"/>
-      <c r="F140" s="108"/>
-      <c r="G140" s="109"/>
+      <c r="F140" s="105"/>
+      <c r="G140" s="106"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
-      <c r="K140" s="110"/>
+      <c r="K140" s="107"/>
       <c r="L140" s="36"/>
-      <c r="M140" s="111"/>
-      <c r="N140" s="112"/>
-      <c r="O140" s="91"/>
+      <c r="M140" s="108"/>
+      <c r="N140" s="109"/>
+      <c r="O140" s="90"/>
       <c r="Q140" s="19"/>
     </row>
     <row r="141" spans="1:17" ht="15.6">
-      <c r="A141" s="107"/>
-      <c r="B141" s="102"/>
+      <c r="A141" s="104"/>
+      <c r="B141" s="99"/>
       <c r="C141" s="75"/>
       <c r="D141" s="43"/>
       <c r="E141" s="30"/>
-      <c r="F141" s="108"/>
-      <c r="G141" s="109"/>
+      <c r="F141" s="105"/>
+      <c r="G141" s="106"/>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
-      <c r="K141" s="110"/>
+      <c r="K141" s="107"/>
       <c r="L141" s="36"/>
-      <c r="M141" s="111"/>
-      <c r="N141" s="112"/>
-      <c r="O141" s="91"/>
+      <c r="M141" s="108"/>
+      <c r="N141" s="109"/>
+      <c r="O141" s="90"/>
       <c r="Q141" s="19"/>
     </row>
     <row r="142" spans="1:17" ht="15.6">
-      <c r="A142" s="107"/>
-      <c r="B142" s="102"/>
+      <c r="A142" s="104"/>
+      <c r="B142" s="99"/>
       <c r="C142" s="75"/>
       <c r="D142" s="43"/>
       <c r="E142" s="30"/>
-      <c r="F142" s="108"/>
-      <c r="G142" s="109"/>
+      <c r="F142" s="105"/>
+      <c r="G142" s="106"/>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
-      <c r="K142" s="110"/>
+      <c r="K142" s="107"/>
       <c r="L142" s="36"/>
-      <c r="M142" s="111"/>
-      <c r="N142" s="112"/>
-      <c r="O142" s="91"/>
+      <c r="M142" s="108"/>
+      <c r="N142" s="109"/>
+      <c r="O142" s="90"/>
       <c r="Q142" s="19"/>
     </row>
     <row r="143" spans="1:17" ht="15.6">
-      <c r="A143" s="107"/>
-      <c r="B143" s="102"/>
+      <c r="A143" s="104"/>
+      <c r="B143" s="99"/>
       <c r="C143" s="75"/>
       <c r="D143" s="43"/>
       <c r="E143" s="30"/>
-      <c r="F143" s="108"/>
-      <c r="G143" s="109"/>
+      <c r="F143" s="105"/>
+      <c r="G143" s="106"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
-      <c r="K143" s="110"/>
+      <c r="K143" s="107"/>
       <c r="L143" s="36"/>
-      <c r="M143" s="111"/>
-      <c r="N143" s="112"/>
-      <c r="O143" s="91"/>
+      <c r="M143" s="108"/>
+      <c r="N143" s="109"/>
+      <c r="O143" s="90"/>
       <c r="Q143" s="19"/>
     </row>
     <row r="144" spans="1:17" ht="15.6">
-      <c r="A144" s="107"/>
-      <c r="B144" s="102"/>
+      <c r="A144" s="104"/>
+      <c r="B144" s="99"/>
       <c r="C144" s="75"/>
       <c r="D144" s="43"/>
       <c r="E144" s="30"/>
-      <c r="F144" s="108"/>
-      <c r="G144" s="109"/>
+      <c r="F144" s="105"/>
+      <c r="G144" s="106"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
-      <c r="K144" s="110"/>
+      <c r="K144" s="107"/>
       <c r="L144" s="36"/>
-      <c r="M144" s="111"/>
-      <c r="N144" s="112"/>
-      <c r="O144" s="91"/>
+      <c r="M144" s="108"/>
+      <c r="N144" s="109"/>
+      <c r="O144" s="90"/>
       <c r="Q144" s="19"/>
     </row>
     <row r="145" spans="1:17" ht="15.6">
-      <c r="A145" s="107"/>
-      <c r="B145" s="102"/>
+      <c r="A145" s="104"/>
+      <c r="B145" s="99"/>
       <c r="C145" s="75"/>
       <c r="D145" s="43"/>
       <c r="E145" s="30"/>
-      <c r="F145" s="108"/>
-      <c r="G145" s="109"/>
+      <c r="F145" s="105"/>
+      <c r="G145" s="106"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
-      <c r="K145" s="110"/>
+      <c r="K145" s="107"/>
       <c r="L145" s="36"/>
-      <c r="M145" s="111"/>
-      <c r="N145" s="112"/>
-      <c r="O145" s="91"/>
+      <c r="M145" s="108"/>
+      <c r="N145" s="109"/>
+      <c r="O145" s="90"/>
       <c r="Q145" s="19"/>
     </row>
     <row r="146" spans="1:17" ht="15.6">
-      <c r="A146" s="107"/>
-      <c r="B146" s="102"/>
+      <c r="A146" s="104"/>
+      <c r="B146" s="99"/>
       <c r="C146" s="75"/>
       <c r="D146" s="43"/>
       <c r="E146" s="30"/>
-      <c r="F146" s="108"/>
-      <c r="G146" s="109"/>
+      <c r="F146" s="105"/>
+      <c r="G146" s="106"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
-      <c r="K146" s="110"/>
+      <c r="K146" s="107"/>
       <c r="L146" s="36"/>
-      <c r="M146" s="111"/>
-      <c r="N146" s="112"/>
-      <c r="O146" s="91"/>
+      <c r="M146" s="108"/>
+      <c r="N146" s="109"/>
+      <c r="O146" s="90"/>
       <c r="Q146" s="19"/>
     </row>
     <row r="147" spans="1:17" ht="15.6">
-      <c r="A147" s="107"/>
-      <c r="B147" s="102"/>
+      <c r="A147" s="104"/>
+      <c r="B147" s="99"/>
       <c r="C147" s="75"/>
       <c r="D147" s="43"/>
       <c r="E147" s="30"/>
-      <c r="F147" s="108"/>
-      <c r="G147" s="109"/>
+      <c r="F147" s="105"/>
+      <c r="G147" s="106"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
-      <c r="K147" s="110"/>
+      <c r="K147" s="107"/>
       <c r="L147" s="36"/>
-      <c r="M147" s="111"/>
+      <c r="M147" s="108"/>
       <c r="N147" s="37"/>
-      <c r="O147" s="91"/>
+      <c r="O147" s="90"/>
       <c r="Q147" s="19"/>
     </row>
     <row r="148" spans="1:17" ht="15.6">
-      <c r="A148" s="107"/>
-      <c r="B148" s="102"/>
+      <c r="A148" s="104"/>
+      <c r="B148" s="99"/>
       <c r="C148" s="75"/>
       <c r="D148" s="43"/>
       <c r="E148" s="30"/>
-      <c r="F148" s="108"/>
-      <c r="G148" s="109"/>
+      <c r="F148" s="105"/>
+      <c r="G148" s="106"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
-      <c r="K148" s="110"/>
+      <c r="K148" s="107"/>
       <c r="L148" s="36"/>
-      <c r="M148" s="111"/>
+      <c r="M148" s="108"/>
       <c r="N148" s="37"/>
-      <c r="O148" s="91"/>
+      <c r="O148" s="90"/>
       <c r="Q148" s="19"/>
     </row>
     <row r="149" spans="1:17" ht="15.6">
-      <c r="A149" s="107"/>
-      <c r="B149" s="102"/>
+      <c r="A149" s="104"/>
+      <c r="B149" s="99"/>
       <c r="C149" s="75"/>
       <c r="D149" s="43"/>
       <c r="E149" s="30"/>
-      <c r="F149" s="108"/>
-      <c r="G149" s="109"/>
+      <c r="F149" s="105"/>
+      <c r="G149" s="106"/>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
-      <c r="K149" s="110"/>
+      <c r="K149" s="107"/>
       <c r="L149" s="36"/>
-      <c r="M149" s="111"/>
+      <c r="M149" s="108"/>
       <c r="N149" s="37"/>
-      <c r="O149" s="91"/>
+      <c r="O149" s="90"/>
       <c r="Q149" s="19"/>
     </row>
     <row r="150" spans="1:17" ht="15.6">
-      <c r="A150" s="107"/>
-      <c r="B150" s="102"/>
+      <c r="A150" s="104"/>
+      <c r="B150" s="99"/>
       <c r="C150" s="75"/>
       <c r="D150" s="43"/>
       <c r="E150" s="30"/>
-      <c r="F150" s="108"/>
-      <c r="G150" s="109"/>
+      <c r="F150" s="105"/>
+      <c r="G150" s="106"/>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
-      <c r="K150" s="110"/>
+      <c r="K150" s="107"/>
       <c r="L150" s="36"/>
-      <c r="M150" s="111"/>
+      <c r="M150" s="108"/>
       <c r="N150" s="37"/>
-      <c r="O150" s="91"/>
+      <c r="O150" s="90"/>
       <c r="Q150" s="19"/>
     </row>
     <row r="151" spans="1:17" ht="15.6">
-      <c r="A151" s="113"/>
+      <c r="A151" s="110"/>
       <c r="B151" s="45"/>
-      <c r="C151" s="114"/>
+      <c r="C151" s="111"/>
       <c r="D151" s="46"/>
       <c r="E151" s="47"/>
-      <c r="F151" s="115"/>
+      <c r="F151" s="112"/>
       <c r="G151" s="47"/>
       <c r="H151" s="7"/>
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
-      <c r="K151" s="116"/>
+      <c r="K151" s="113"/>
       <c r="L151" s="50"/>
-      <c r="M151" s="117"/>
+      <c r="M151" s="114"/>
       <c r="N151" s="50"/>
-      <c r="Q151" s="118"/>
+      <c r="Q151" s="115"/>
     </row>
     <row r="152" spans="1:17">
       <c r="B152" s="51"/>
       <c r="H152" s="9"/>
       <c r="I152" s="9"/>
       <c r="J152" s="9"/>
-      <c r="K152" s="119"/>
+      <c r="K152" s="116"/>
     </row>
     <row r="153" spans="1:17" ht="15" thickBot="1">
       <c r="B153" s="51"/>
@@ -7273,7 +7267,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K153" s="121"/>
+      <c r="K153" s="118"/>
       <c r="L153" s="11">
         <f>SUM(H153:K153)</f>
         <v>0</v>
@@ -7283,14 +7277,14 @@
       <c r="H154" s="12"/>
       <c r="I154" s="12"/>
       <c r="J154" s="12"/>
-      <c r="K154" s="119"/>
+      <c r="K154" s="116"/>
     </row>
     <row r="155" spans="1:17" s="19" customFormat="1">
       <c r="C155" s="55"/>
       <c r="D155" s="40"/>
       <c r="H155" s="54"/>
-      <c r="K155" s="122"/>
-      <c r="M155" s="120"/>
+      <c r="K155" s="119"/>
+      <c r="M155" s="117"/>
       <c r="O155" s="16"/>
       <c r="P155" s="16"/>
       <c r="Q155" s="16"/>
@@ -7355,16 +7349,16 @@
       <c r="D6" s="58"/>
       <c r="E6" s="58"/>
       <c r="F6" s="58"/>
-      <c r="G6" s="192" t="s">
+      <c r="G6" s="213" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="193"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="123"/>
+      <c r="H6" s="214"/>
+      <c r="I6" s="215"/>
+      <c r="J6" s="120"/>
       <c r="K6" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="124"/>
+      <c r="L6" s="121"/>
       <c r="M6" s="58"/>
     </row>
     <row r="7" spans="1:16" s="64" customFormat="1" ht="57.6">
@@ -7392,10 +7386,10 @@
       <c r="H7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="126" t="s">
+      <c r="J7" s="123" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="70" t="s">
@@ -7407,13 +7401,13 @@
       <c r="M7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="127"/>
+      <c r="N7" s="124"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="124"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="78"/>
-      <c r="B8" s="128"/>
+      <c r="B8" s="125"/>
       <c r="C8" s="25"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
@@ -7427,214 +7421,214 @@
       <c r="I8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="129"/>
+      <c r="J8" s="126"/>
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="130"/>
+      <c r="A9" s="127"/>
       <c r="B9" s="15"/>
-      <c r="C9" s="131"/>
+      <c r="C9" s="128"/>
       <c r="D9" s="43"/>
       <c r="E9" s="43"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="129"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="133"/>
+      <c r="K9" s="130"/>
       <c r="L9" s="37"/>
-      <c r="M9" s="197"/>
+      <c r="M9" s="188"/>
       <c r="P9" s="19"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="130"/>
+      <c r="A10" s="127"/>
       <c r="B10" s="15"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="133"/>
+      <c r="K10" s="130"/>
       <c r="L10" s="37"/>
       <c r="M10" s="37"/>
       <c r="P10" s="19"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="130"/>
+      <c r="A11" s="127"/>
       <c r="B11" s="15"/>
-      <c r="C11" s="131"/>
+      <c r="C11" s="128"/>
       <c r="D11" s="43"/>
       <c r="E11" s="43"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="129"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="135"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="132"/>
       <c r="M11" s="37"/>
-      <c r="P11" s="136"/>
+      <c r="P11" s="133"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="130"/>
+      <c r="A12" s="127"/>
       <c r="B12" s="15"/>
-      <c r="C12" s="131"/>
+      <c r="C12" s="128"/>
       <c r="D12" s="43"/>
       <c r="E12" s="43"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="132"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="133"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="134"/>
+      <c r="K12" s="130"/>
       <c r="L12" s="37"/>
       <c r="M12" s="37"/>
       <c r="P12" s="19"/>
     </row>
     <row r="13" spans="1:16" ht="14.1" customHeight="1">
-      <c r="A13" s="130"/>
+      <c r="A13" s="127"/>
       <c r="B13" s="15"/>
-      <c r="C13" s="131"/>
+      <c r="C13" s="128"/>
       <c r="D13" s="43"/>
       <c r="E13" s="43"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="195"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="196"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="186"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="187"/>
       <c r="M13" s="37"/>
       <c r="P13" s="19"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="130"/>
+      <c r="A14" s="127"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="131"/>
+      <c r="C14" s="128"/>
       <c r="D14" s="43"/>
       <c r="E14" s="43"/>
-      <c r="F14" s="108"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="133"/>
-      <c r="L14" s="135"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="132"/>
       <c r="M14" s="37"/>
       <c r="P14" s="19"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="130"/>
+      <c r="A15" s="127"/>
       <c r="B15" s="15"/>
-      <c r="C15" s="131"/>
+      <c r="C15" s="128"/>
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="129"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="135"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="132"/>
       <c r="M15" s="37"/>
       <c r="P15" s="19"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="130"/>
+      <c r="A16" s="127"/>
       <c r="B16" s="15"/>
-      <c r="C16" s="131"/>
+      <c r="C16" s="128"/>
       <c r="D16" s="43"/>
       <c r="E16" s="43"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="129"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="133"/>
+      <c r="K16" s="130"/>
       <c r="L16" s="37"/>
       <c r="M16" s="37"/>
-      <c r="N16" s="139"/>
+      <c r="N16" s="136"/>
       <c r="P16" s="19"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="130"/>
+      <c r="A17" s="127"/>
       <c r="B17" s="15"/>
-      <c r="C17" s="131"/>
+      <c r="C17" s="128"/>
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="132"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="132"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="133"/>
+      <c r="K17" s="130"/>
       <c r="L17" s="37"/>
-      <c r="M17" s="133"/>
+      <c r="M17" s="130"/>
       <c r="P17" s="19"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="130"/>
+      <c r="A18" s="127"/>
       <c r="B18" s="15"/>
-      <c r="C18" s="131"/>
+      <c r="C18" s="128"/>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="132"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="129"/>
+      <c r="I18" s="129"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="133"/>
+      <c r="K18" s="130"/>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
       <c r="P18" s="19"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="130"/>
+      <c r="A19" s="127"/>
       <c r="B19" s="15"/>
-      <c r="C19" s="131"/>
+      <c r="C19" s="128"/>
       <c r="D19" s="43"/>
       <c r="E19" s="43"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="132"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="129"/>
+      <c r="I19" s="129"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="133"/>
+      <c r="K19" s="130"/>
       <c r="L19" s="37"/>
       <c r="M19" s="37"/>
       <c r="P19" s="19"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="130"/>
+      <c r="A20" s="127"/>
       <c r="B20" s="15"/>
-      <c r="C20" s="131"/>
+      <c r="C20" s="128"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
       <c r="J20" s="6"/>
-      <c r="K20" s="133"/>
+      <c r="K20" s="130"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
       <c r="P20" s="19"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="130"/>
+      <c r="A21" s="127"/>
       <c r="B21" s="15"/>
-      <c r="C21" s="131"/>
+      <c r="C21" s="128"/>
       <c r="D21" s="43"/>
       <c r="E21" s="43"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
       <c r="J21" s="6"/>
       <c r="K21" s="16"/>
       <c r="L21" s="37"/>
@@ -7642,891 +7636,891 @@
       <c r="P21" s="19"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="130"/>
+      <c r="A22" s="127"/>
       <c r="B22" s="15"/>
-      <c r="C22" s="131"/>
+      <c r="C22" s="128"/>
       <c r="D22" s="43"/>
       <c r="E22" s="43"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="129"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="133"/>
+      <c r="K22" s="130"/>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
       <c r="P22" s="19"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="130"/>
+      <c r="A23" s="127"/>
       <c r="B23" s="15"/>
-      <c r="C23" s="131"/>
+      <c r="C23" s="128"/>
       <c r="D23" s="43"/>
       <c r="E23" s="43"/>
-      <c r="F23" s="108"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="132"/>
-      <c r="I23" s="132"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
       <c r="J23" s="6"/>
-      <c r="K23" s="133"/>
+      <c r="K23" s="130"/>
       <c r="L23" s="37"/>
       <c r="M23" s="37"/>
       <c r="P23" s="19"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="130"/>
+      <c r="A24" s="127"/>
       <c r="B24" s="15"/>
-      <c r="C24" s="131"/>
+      <c r="C24" s="128"/>
       <c r="D24" s="43"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="132"/>
-      <c r="I24" s="132"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="133"/>
+      <c r="K24" s="130"/>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="P24" s="19"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="130"/>
+      <c r="A25" s="127"/>
       <c r="B25" s="15"/>
-      <c r="C25" s="131"/>
+      <c r="C25" s="128"/>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="129"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="129"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="133"/>
+      <c r="K25" s="130"/>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
       <c r="P25" s="19"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="130"/>
+      <c r="A26" s="127"/>
       <c r="B26" s="15"/>
-      <c r="C26" s="131"/>
+      <c r="C26" s="128"/>
       <c r="D26" s="43"/>
       <c r="E26" s="43"/>
-      <c r="F26" s="108"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="129"/>
+      <c r="I26" s="129"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="133"/>
+      <c r="K26" s="130"/>
       <c r="L26" s="37"/>
-      <c r="M26" s="140"/>
+      <c r="M26" s="137"/>
       <c r="P26" s="19"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="130"/>
+      <c r="A27" s="127"/>
       <c r="B27" s="15"/>
-      <c r="C27" s="131"/>
+      <c r="C27" s="128"/>
       <c r="D27" s="43"/>
       <c r="E27" s="43"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="132"/>
-      <c r="I27" s="132"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="129"/>
+      <c r="I27" s="129"/>
       <c r="J27" s="6"/>
-      <c r="K27" s="133"/>
+      <c r="K27" s="130"/>
       <c r="L27" s="37"/>
-      <c r="M27" s="112"/>
+      <c r="M27" s="109"/>
       <c r="P27" s="19"/>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="130"/>
+      <c r="A28" s="127"/>
       <c r="B28" s="15"/>
-      <c r="C28" s="131"/>
+      <c r="C28" s="128"/>
       <c r="D28" s="43"/>
       <c r="E28" s="43"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="132"/>
-      <c r="I28" s="132"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="129"/>
       <c r="J28" s="6"/>
-      <c r="K28" s="133"/>
+      <c r="K28" s="130"/>
       <c r="L28" s="37"/>
       <c r="M28" s="37"/>
       <c r="P28" s="19"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="130"/>
+      <c r="A29" s="127"/>
       <c r="B29" s="15"/>
-      <c r="C29" s="131"/>
+      <c r="C29" s="128"/>
       <c r="D29" s="43"/>
       <c r="E29" s="43"/>
-      <c r="F29" s="108"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="132"/>
-      <c r="I29" s="132"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="129"/>
+      <c r="I29" s="129"/>
       <c r="J29" s="6"/>
-      <c r="K29" s="133"/>
+      <c r="K29" s="130"/>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
       <c r="P29" s="19"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="130"/>
+      <c r="A30" s="127"/>
       <c r="B30" s="15"/>
-      <c r="C30" s="131"/>
+      <c r="C30" s="128"/>
       <c r="D30" s="43"/>
       <c r="E30" s="43"/>
-      <c r="F30" s="108"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="132"/>
-      <c r="I30" s="132"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="129"/>
       <c r="J30" s="6"/>
-      <c r="K30" s="133"/>
+      <c r="K30" s="130"/>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
       <c r="P30" s="19"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="130"/>
+      <c r="A31" s="127"/>
       <c r="B31" s="15"/>
-      <c r="C31" s="131"/>
+      <c r="C31" s="128"/>
       <c r="D31" s="43"/>
       <c r="E31" s="43"/>
-      <c r="F31" s="108"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="195"/>
-      <c r="K31" s="133"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="129"/>
+      <c r="H31" s="129"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="186"/>
+      <c r="K31" s="130"/>
       <c r="L31" s="37"/>
       <c r="M31" s="37"/>
       <c r="P31" s="19"/>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="130"/>
+      <c r="A32" s="127"/>
       <c r="B32" s="15"/>
-      <c r="C32" s="131"/>
+      <c r="C32" s="128"/>
       <c r="D32" s="43"/>
       <c r="E32" s="43"/>
-      <c r="F32" s="108"/>
-      <c r="G32" s="132"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="129"/>
+      <c r="H32" s="129"/>
+      <c r="I32" s="129"/>
       <c r="J32" s="6"/>
-      <c r="K32" s="133"/>
+      <c r="K32" s="130"/>
       <c r="L32" s="37"/>
       <c r="M32" s="37"/>
       <c r="P32" s="19"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="130"/>
+      <c r="A33" s="127"/>
       <c r="B33" s="15"/>
-      <c r="C33" s="131"/>
+      <c r="C33" s="128"/>
       <c r="D33" s="43"/>
       <c r="E33" s="43"/>
-      <c r="F33" s="108"/>
-      <c r="G33" s="132"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="129"/>
+      <c r="I33" s="129"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="133"/>
+      <c r="K33" s="130"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37"/>
       <c r="P33" s="19"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="130"/>
+      <c r="A34" s="127"/>
       <c r="B34" s="15"/>
-      <c r="C34" s="131"/>
+      <c r="C34" s="128"/>
       <c r="D34" s="43"/>
       <c r="E34" s="43"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="132"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="129"/>
+      <c r="I34" s="129"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="133"/>
+      <c r="K34" s="130"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
       <c r="P34" s="19"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="130"/>
+      <c r="A35" s="127"/>
       <c r="B35" s="15"/>
-      <c r="C35" s="131"/>
+      <c r="C35" s="128"/>
       <c r="D35" s="43"/>
       <c r="E35" s="43"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="132"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="129"/>
+      <c r="H35" s="129"/>
+      <c r="I35" s="129"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="133"/>
+      <c r="K35" s="130"/>
       <c r="L35" s="37"/>
       <c r="M35" s="37"/>
       <c r="P35" s="19"/>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="130"/>
+      <c r="A36" s="127"/>
       <c r="B36" s="15"/>
-      <c r="C36" s="131"/>
+      <c r="C36" s="128"/>
       <c r="D36" s="43"/>
       <c r="E36" s="43"/>
-      <c r="F36" s="108"/>
-      <c r="G36" s="132"/>
-      <c r="H36" s="132"/>
-      <c r="I36" s="132"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="129"/>
+      <c r="H36" s="129"/>
+      <c r="I36" s="129"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="133"/>
+      <c r="K36" s="130"/>
       <c r="L36" s="37"/>
       <c r="M36" s="37"/>
       <c r="P36" s="19"/>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="130"/>
+      <c r="A37" s="127"/>
       <c r="B37" s="15"/>
-      <c r="C37" s="131"/>
+      <c r="C37" s="128"/>
       <c r="D37" s="43"/>
       <c r="E37" s="43"/>
-      <c r="F37" s="108"/>
-      <c r="G37" s="132"/>
-      <c r="H37" s="132"/>
-      <c r="I37" s="132"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="129"/>
+      <c r="H37" s="129"/>
+      <c r="I37" s="129"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="133"/>
+      <c r="K37" s="130"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
       <c r="P37" s="19"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="130"/>
+      <c r="A38" s="127"/>
       <c r="B38" s="15"/>
-      <c r="C38" s="131"/>
+      <c r="C38" s="128"/>
       <c r="D38" s="43"/>
       <c r="E38" s="43"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="132"/>
-      <c r="H38" s="132"/>
-      <c r="I38" s="132"/>
-      <c r="J38" s="195"/>
-      <c r="K38" s="133"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="129"/>
+      <c r="H38" s="129"/>
+      <c r="I38" s="129"/>
+      <c r="J38" s="186"/>
+      <c r="K38" s="130"/>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
       <c r="P38" s="19"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="130"/>
+      <c r="A39" s="127"/>
       <c r="B39" s="15"/>
-      <c r="C39" s="131"/>
+      <c r="C39" s="128"/>
       <c r="D39" s="43"/>
       <c r="E39" s="43"/>
-      <c r="F39" s="108"/>
-      <c r="G39" s="132"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="129"/>
+      <c r="H39" s="129"/>
+      <c r="I39" s="129"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="133"/>
+      <c r="K39" s="130"/>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
       <c r="P39" s="19"/>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="130"/>
+      <c r="A40" s="127"/>
       <c r="B40" s="15"/>
-      <c r="C40" s="131"/>
+      <c r="C40" s="128"/>
       <c r="D40" s="43"/>
       <c r="E40" s="43"/>
-      <c r="F40" s="108"/>
-      <c r="G40" s="132"/>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="129"/>
+      <c r="I40" s="129"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="133"/>
+      <c r="K40" s="130"/>
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
       <c r="P40" s="19"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="130"/>
+      <c r="A41" s="127"/>
       <c r="B41" s="15"/>
-      <c r="C41" s="131"/>
+      <c r="C41" s="128"/>
       <c r="D41" s="43"/>
       <c r="E41" s="43"/>
-      <c r="F41" s="108"/>
-      <c r="G41" s="132"/>
-      <c r="H41" s="132"/>
-      <c r="I41" s="132"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="129"/>
+      <c r="I41" s="129"/>
       <c r="J41" s="6"/>
-      <c r="K41" s="133"/>
+      <c r="K41" s="130"/>
       <c r="L41" s="37"/>
       <c r="M41" s="37"/>
       <c r="P41" s="19"/>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="130"/>
+      <c r="A42" s="127"/>
       <c r="B42" s="15"/>
-      <c r="C42" s="131"/>
+      <c r="C42" s="128"/>
       <c r="D42" s="43"/>
       <c r="E42" s="43"/>
-      <c r="F42" s="108"/>
-      <c r="G42" s="132"/>
-      <c r="H42" s="132"/>
-      <c r="I42" s="132"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="129"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="129"/>
       <c r="J42" s="6"/>
-      <c r="K42" s="133"/>
+      <c r="K42" s="130"/>
       <c r="L42" s="37"/>
       <c r="M42" s="37"/>
       <c r="P42" s="19"/>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="130"/>
+      <c r="A43" s="127"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="131"/>
+      <c r="C43" s="128"/>
       <c r="D43" s="43"/>
       <c r="E43" s="43"/>
-      <c r="F43" s="108"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
       <c r="J43" s="6"/>
-      <c r="K43" s="133"/>
+      <c r="K43" s="130"/>
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
       <c r="P43" s="19"/>
     </row>
     <row r="44" spans="1:16" hidden="1">
-      <c r="A44" s="130"/>
+      <c r="A44" s="127"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="131"/>
+      <c r="C44" s="128"/>
       <c r="D44" s="43"/>
       <c r="E44" s="43"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="132"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="129"/>
       <c r="J44" s="6"/>
-      <c r="K44" s="133"/>
+      <c r="K44" s="130"/>
       <c r="L44" s="37"/>
       <c r="M44" s="37"/>
       <c r="P44" s="19"/>
     </row>
     <row r="45" spans="1:16" hidden="1">
-      <c r="A45" s="130"/>
+      <c r="A45" s="127"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="131"/>
+      <c r="C45" s="128"/>
       <c r="D45" s="43"/>
       <c r="E45" s="43"/>
-      <c r="F45" s="108"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="132"/>
-      <c r="I45" s="132"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="129"/>
+      <c r="H45" s="129"/>
+      <c r="I45" s="129"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="133"/>
+      <c r="K45" s="130"/>
       <c r="L45" s="37"/>
       <c r="M45" s="37"/>
       <c r="P45" s="19"/>
     </row>
     <row r="46" spans="1:16" hidden="1">
-      <c r="A46" s="130"/>
+      <c r="A46" s="127"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="131"/>
+      <c r="C46" s="128"/>
       <c r="D46" s="43"/>
       <c r="E46" s="43"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="132"/>
-      <c r="H46" s="132"/>
-      <c r="I46" s="132"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="129"/>
+      <c r="H46" s="129"/>
+      <c r="I46" s="129"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="133"/>
+      <c r="K46" s="130"/>
       <c r="L46" s="37"/>
       <c r="M46" s="37"/>
       <c r="P46" s="19"/>
     </row>
     <row r="47" spans="1:16" hidden="1">
-      <c r="A47" s="130"/>
+      <c r="A47" s="127"/>
       <c r="B47" s="15"/>
-      <c r="C47" s="131"/>
+      <c r="C47" s="128"/>
       <c r="D47" s="43"/>
       <c r="E47" s="43"/>
-      <c r="F47" s="108"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="132"/>
-      <c r="I47" s="132"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="129"/>
+      <c r="H47" s="129"/>
+      <c r="I47" s="129"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="133"/>
+      <c r="K47" s="130"/>
       <c r="L47" s="37"/>
       <c r="M47" s="37"/>
       <c r="P47" s="19"/>
     </row>
     <row r="48" spans="1:16" hidden="1">
-      <c r="A48" s="130"/>
+      <c r="A48" s="127"/>
       <c r="B48" s="15"/>
-      <c r="C48" s="131"/>
+      <c r="C48" s="128"/>
       <c r="D48" s="43"/>
       <c r="E48" s="43"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="132"/>
-      <c r="H48" s="132"/>
-      <c r="I48" s="132"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="129"/>
+      <c r="H48" s="129"/>
+      <c r="I48" s="129"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="133"/>
+      <c r="K48" s="130"/>
       <c r="L48" s="37"/>
       <c r="M48" s="37"/>
       <c r="P48" s="19"/>
     </row>
     <row r="49" spans="1:16" hidden="1">
-      <c r="A49" s="130"/>
+      <c r="A49" s="127"/>
       <c r="B49" s="15"/>
-      <c r="C49" s="131"/>
+      <c r="C49" s="128"/>
       <c r="D49" s="43"/>
       <c r="E49" s="43"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="132"/>
-      <c r="I49" s="132"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="129"/>
+      <c r="H49" s="129"/>
+      <c r="I49" s="129"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="133"/>
+      <c r="K49" s="130"/>
       <c r="L49" s="37"/>
       <c r="M49" s="37"/>
       <c r="P49" s="19"/>
     </row>
     <row r="50" spans="1:16" hidden="1">
-      <c r="A50" s="130"/>
+      <c r="A50" s="127"/>
       <c r="B50" s="15"/>
-      <c r="C50" s="131"/>
+      <c r="C50" s="128"/>
       <c r="D50" s="43"/>
       <c r="E50" s="43"/>
-      <c r="F50" s="108"/>
-      <c r="G50" s="132"/>
-      <c r="H50" s="132"/>
-      <c r="I50" s="132"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="129"/>
+      <c r="H50" s="129"/>
+      <c r="I50" s="129"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="133"/>
+      <c r="K50" s="130"/>
       <c r="L50" s="37"/>
       <c r="M50" s="37"/>
       <c r="P50" s="19"/>
     </row>
     <row r="51" spans="1:16" hidden="1">
-      <c r="A51" s="130"/>
+      <c r="A51" s="127"/>
       <c r="B51" s="15"/>
-      <c r="C51" s="131"/>
+      <c r="C51" s="128"/>
       <c r="D51" s="43"/>
       <c r="E51" s="43"/>
-      <c r="F51" s="108"/>
-      <c r="G51" s="132"/>
-      <c r="H51" s="132"/>
-      <c r="I51" s="132"/>
+      <c r="F51" s="105"/>
+      <c r="G51" s="129"/>
+      <c r="H51" s="129"/>
+      <c r="I51" s="129"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="133"/>
+      <c r="K51" s="130"/>
       <c r="L51" s="37"/>
       <c r="M51" s="37"/>
       <c r="P51" s="19"/>
     </row>
     <row r="52" spans="1:16" hidden="1">
-      <c r="A52" s="130"/>
+      <c r="A52" s="127"/>
       <c r="B52" s="15"/>
-      <c r="C52" s="131"/>
+      <c r="C52" s="128"/>
       <c r="D52" s="43"/>
       <c r="E52" s="43"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="132"/>
-      <c r="H52" s="132"/>
-      <c r="I52" s="132"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="129"/>
+      <c r="H52" s="129"/>
+      <c r="I52" s="129"/>
       <c r="J52" s="6"/>
-      <c r="K52" s="133"/>
+      <c r="K52" s="130"/>
       <c r="L52" s="37"/>
       <c r="M52" s="37"/>
       <c r="P52" s="19"/>
     </row>
     <row r="53" spans="1:16" hidden="1">
-      <c r="A53" s="130"/>
+      <c r="A53" s="127"/>
       <c r="B53" s="15"/>
-      <c r="C53" s="131"/>
+      <c r="C53" s="128"/>
       <c r="D53" s="43"/>
       <c r="E53" s="43"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="132"/>
-      <c r="H53" s="132"/>
-      <c r="I53" s="132"/>
+      <c r="F53" s="105"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="129"/>
+      <c r="I53" s="129"/>
       <c r="J53" s="6"/>
-      <c r="K53" s="133"/>
+      <c r="K53" s="130"/>
       <c r="L53" s="37"/>
       <c r="M53" s="37"/>
       <c r="P53" s="19"/>
     </row>
     <row r="54" spans="1:16" hidden="1">
-      <c r="A54" s="130"/>
+      <c r="A54" s="127"/>
       <c r="B54" s="15"/>
-      <c r="C54" s="131"/>
+      <c r="C54" s="128"/>
       <c r="D54" s="43"/>
       <c r="E54" s="43"/>
-      <c r="F54" s="108"/>
-      <c r="G54" s="132"/>
-      <c r="H54" s="132"/>
-      <c r="I54" s="132"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="129"/>
+      <c r="H54" s="129"/>
+      <c r="I54" s="129"/>
       <c r="J54" s="6"/>
-      <c r="K54" s="133"/>
+      <c r="K54" s="130"/>
       <c r="L54" s="37"/>
       <c r="M54" s="37"/>
       <c r="P54" s="19"/>
     </row>
     <row r="55" spans="1:16" hidden="1">
-      <c r="A55" s="130"/>
+      <c r="A55" s="127"/>
       <c r="B55" s="15"/>
-      <c r="C55" s="131"/>
+      <c r="C55" s="128"/>
       <c r="D55" s="43"/>
       <c r="E55" s="43"/>
-      <c r="F55" s="108"/>
-      <c r="G55" s="132"/>
-      <c r="H55" s="132"/>
-      <c r="I55" s="132"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="129"/>
+      <c r="H55" s="129"/>
+      <c r="I55" s="129"/>
       <c r="J55" s="6"/>
-      <c r="K55" s="133"/>
+      <c r="K55" s="130"/>
       <c r="L55" s="37"/>
       <c r="M55" s="37"/>
       <c r="P55" s="19"/>
     </row>
     <row r="56" spans="1:16" hidden="1">
-      <c r="A56" s="130"/>
+      <c r="A56" s="127"/>
       <c r="B56" s="15"/>
-      <c r="C56" s="131"/>
+      <c r="C56" s="128"/>
       <c r="D56" s="43"/>
       <c r="E56" s="43"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="132"/>
-      <c r="H56" s="132"/>
-      <c r="I56" s="132"/>
+      <c r="F56" s="105"/>
+      <c r="G56" s="129"/>
+      <c r="H56" s="129"/>
+      <c r="I56" s="129"/>
       <c r="J56" s="6"/>
-      <c r="K56" s="133"/>
+      <c r="K56" s="130"/>
       <c r="L56" s="37"/>
       <c r="M56" s="37"/>
       <c r="P56" s="19"/>
     </row>
     <row r="57" spans="1:16" hidden="1">
-      <c r="A57" s="130"/>
+      <c r="A57" s="127"/>
       <c r="B57" s="15"/>
-      <c r="C57" s="131"/>
+      <c r="C57" s="128"/>
       <c r="D57" s="43"/>
       <c r="E57" s="43"/>
-      <c r="F57" s="108"/>
-      <c r="G57" s="132"/>
-      <c r="H57" s="132"/>
-      <c r="I57" s="132"/>
+      <c r="F57" s="105"/>
+      <c r="G57" s="129"/>
+      <c r="H57" s="129"/>
+      <c r="I57" s="129"/>
       <c r="J57" s="6"/>
-      <c r="K57" s="133"/>
+      <c r="K57" s="130"/>
       <c r="L57" s="37"/>
       <c r="M57" s="37"/>
       <c r="P57" s="19"/>
     </row>
     <row r="58" spans="1:16" hidden="1">
-      <c r="A58" s="130"/>
+      <c r="A58" s="127"/>
       <c r="B58" s="15"/>
-      <c r="C58" s="131"/>
+      <c r="C58" s="128"/>
       <c r="D58" s="43"/>
       <c r="E58" s="43"/>
-      <c r="F58" s="108"/>
-      <c r="G58" s="132"/>
-      <c r="H58" s="132"/>
-      <c r="I58" s="132"/>
+      <c r="F58" s="105"/>
+      <c r="G58" s="129"/>
+      <c r="H58" s="129"/>
+      <c r="I58" s="129"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="133"/>
+      <c r="K58" s="130"/>
       <c r="L58" s="37"/>
       <c r="M58" s="37"/>
       <c r="P58" s="19"/>
     </row>
     <row r="59" spans="1:16" hidden="1">
-      <c r="A59" s="130"/>
+      <c r="A59" s="127"/>
       <c r="B59" s="15"/>
-      <c r="C59" s="131"/>
+      <c r="C59" s="128"/>
       <c r="D59" s="43"/>
       <c r="E59" s="43"/>
-      <c r="F59" s="108"/>
-      <c r="G59" s="132"/>
-      <c r="H59" s="132"/>
-      <c r="I59" s="132"/>
+      <c r="F59" s="105"/>
+      <c r="G59" s="129"/>
+      <c r="H59" s="129"/>
+      <c r="I59" s="129"/>
       <c r="J59" s="6"/>
-      <c r="K59" s="133"/>
+      <c r="K59" s="130"/>
       <c r="L59" s="37"/>
       <c r="M59" s="37"/>
       <c r="P59" s="19"/>
     </row>
     <row r="60" spans="1:16" hidden="1">
-      <c r="A60" s="130"/>
+      <c r="A60" s="127"/>
       <c r="B60" s="15"/>
-      <c r="C60" s="131"/>
+      <c r="C60" s="128"/>
       <c r="D60" s="43"/>
       <c r="E60" s="43"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="132"/>
-      <c r="H60" s="132"/>
-      <c r="I60" s="132"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="129"/>
+      <c r="H60" s="129"/>
+      <c r="I60" s="129"/>
       <c r="J60" s="6"/>
-      <c r="K60" s="133"/>
+      <c r="K60" s="130"/>
       <c r="L60" s="37"/>
       <c r="M60" s="37"/>
       <c r="P60" s="19"/>
     </row>
     <row r="61" spans="1:16" hidden="1">
-      <c r="A61" s="130"/>
+      <c r="A61" s="127"/>
       <c r="B61" s="15"/>
-      <c r="C61" s="131"/>
+      <c r="C61" s="128"/>
       <c r="D61" s="43"/>
       <c r="E61" s="43"/>
-      <c r="F61" s="108"/>
-      <c r="G61" s="132"/>
-      <c r="H61" s="132"/>
-      <c r="I61" s="132"/>
+      <c r="F61" s="105"/>
+      <c r="G61" s="129"/>
+      <c r="H61" s="129"/>
+      <c r="I61" s="129"/>
       <c r="J61" s="6"/>
-      <c r="K61" s="133"/>
+      <c r="K61" s="130"/>
       <c r="L61" s="37"/>
       <c r="M61" s="37"/>
       <c r="P61" s="19"/>
     </row>
     <row r="62" spans="1:16" hidden="1">
-      <c r="A62" s="130"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="15"/>
-      <c r="C62" s="131"/>
+      <c r="C62" s="128"/>
       <c r="D62" s="43"/>
       <c r="E62" s="43"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="132"/>
-      <c r="H62" s="132"/>
-      <c r="I62" s="132"/>
+      <c r="F62" s="105"/>
+      <c r="G62" s="129"/>
+      <c r="H62" s="129"/>
+      <c r="I62" s="129"/>
       <c r="J62" s="6"/>
-      <c r="K62" s="133"/>
+      <c r="K62" s="130"/>
       <c r="L62" s="37"/>
       <c r="M62" s="37"/>
       <c r="P62" s="19"/>
     </row>
     <row r="63" spans="1:16" hidden="1">
-      <c r="A63" s="130"/>
+      <c r="A63" s="127"/>
       <c r="B63" s="15"/>
-      <c r="C63" s="131"/>
+      <c r="C63" s="128"/>
       <c r="D63" s="43"/>
       <c r="E63" s="43"/>
-      <c r="F63" s="108"/>
-      <c r="G63" s="132"/>
-      <c r="H63" s="132"/>
-      <c r="I63" s="132"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="129"/>
+      <c r="H63" s="129"/>
+      <c r="I63" s="129"/>
       <c r="J63" s="6"/>
-      <c r="K63" s="133"/>
+      <c r="K63" s="130"/>
       <c r="L63" s="37"/>
       <c r="M63" s="37"/>
       <c r="P63" s="19"/>
     </row>
     <row r="64" spans="1:16" hidden="1">
-      <c r="A64" s="130"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="15"/>
-      <c r="C64" s="131"/>
+      <c r="C64" s="128"/>
       <c r="D64" s="43"/>
       <c r="E64" s="43"/>
-      <c r="F64" s="108"/>
-      <c r="G64" s="132"/>
-      <c r="H64" s="132"/>
-      <c r="I64" s="132"/>
+      <c r="F64" s="105"/>
+      <c r="G64" s="129"/>
+      <c r="H64" s="129"/>
+      <c r="I64" s="129"/>
       <c r="J64" s="6"/>
-      <c r="K64" s="133"/>
+      <c r="K64" s="130"/>
       <c r="L64" s="37"/>
       <c r="M64" s="37"/>
       <c r="P64" s="19"/>
     </row>
     <row r="65" spans="1:16" hidden="1">
-      <c r="A65" s="130"/>
+      <c r="A65" s="127"/>
       <c r="B65" s="15"/>
-      <c r="C65" s="131"/>
+      <c r="C65" s="128"/>
       <c r="D65" s="43"/>
       <c r="E65" s="43"/>
-      <c r="F65" s="108"/>
-      <c r="G65" s="132"/>
-      <c r="H65" s="132"/>
-      <c r="I65" s="132"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="129"/>
+      <c r="H65" s="129"/>
+      <c r="I65" s="129"/>
       <c r="J65" s="6"/>
-      <c r="K65" s="133"/>
+      <c r="K65" s="130"/>
       <c r="L65" s="37"/>
       <c r="M65" s="37"/>
       <c r="P65" s="19"/>
     </row>
     <row r="66" spans="1:16" hidden="1">
-      <c r="A66" s="130"/>
+      <c r="A66" s="127"/>
       <c r="B66" s="15"/>
-      <c r="C66" s="131"/>
+      <c r="C66" s="128"/>
       <c r="D66" s="43"/>
       <c r="E66" s="43"/>
-      <c r="F66" s="108"/>
-      <c r="G66" s="132"/>
-      <c r="H66" s="132"/>
-      <c r="I66" s="132"/>
+      <c r="F66" s="105"/>
+      <c r="G66" s="129"/>
+      <c r="H66" s="129"/>
+      <c r="I66" s="129"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="133"/>
+      <c r="K66" s="130"/>
       <c r="L66" s="37"/>
       <c r="M66" s="37"/>
       <c r="P66" s="19"/>
     </row>
     <row r="67" spans="1:16" hidden="1">
-      <c r="A67" s="130"/>
+      <c r="A67" s="127"/>
       <c r="B67" s="15"/>
-      <c r="C67" s="131"/>
+      <c r="C67" s="128"/>
       <c r="D67" s="43"/>
       <c r="E67" s="43"/>
-      <c r="F67" s="108"/>
-      <c r="G67" s="132"/>
-      <c r="H67" s="132"/>
-      <c r="I67" s="132"/>
+      <c r="F67" s="105"/>
+      <c r="G67" s="129"/>
+      <c r="H67" s="129"/>
+      <c r="I67" s="129"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="133"/>
+      <c r="K67" s="130"/>
       <c r="L67" s="37"/>
       <c r="M67" s="37"/>
       <c r="P67" s="19"/>
     </row>
     <row r="68" spans="1:16" hidden="1">
-      <c r="A68" s="130"/>
+      <c r="A68" s="127"/>
       <c r="B68" s="15"/>
-      <c r="C68" s="131"/>
+      <c r="C68" s="128"/>
       <c r="D68" s="43"/>
       <c r="E68" s="43"/>
-      <c r="F68" s="108"/>
-      <c r="G68" s="132"/>
-      <c r="H68" s="132"/>
-      <c r="I68" s="132"/>
+      <c r="F68" s="105"/>
+      <c r="G68" s="129"/>
+      <c r="H68" s="129"/>
+      <c r="I68" s="129"/>
       <c r="J68" s="6"/>
-      <c r="K68" s="133"/>
+      <c r="K68" s="130"/>
       <c r="L68" s="37"/>
       <c r="M68" s="37"/>
       <c r="P68" s="19"/>
     </row>
     <row r="69" spans="1:16" hidden="1">
-      <c r="A69" s="130"/>
+      <c r="A69" s="127"/>
       <c r="B69" s="15"/>
-      <c r="C69" s="131"/>
+      <c r="C69" s="128"/>
       <c r="D69" s="43"/>
       <c r="E69" s="43"/>
-      <c r="F69" s="108"/>
-      <c r="G69" s="132"/>
-      <c r="H69" s="132"/>
-      <c r="I69" s="132"/>
+      <c r="F69" s="105"/>
+      <c r="G69" s="129"/>
+      <c r="H69" s="129"/>
+      <c r="I69" s="129"/>
       <c r="J69" s="6"/>
-      <c r="K69" s="133"/>
+      <c r="K69" s="130"/>
       <c r="L69" s="37"/>
       <c r="M69" s="37"/>
       <c r="P69" s="19"/>
     </row>
     <row r="70" spans="1:16" hidden="1">
-      <c r="A70" s="130"/>
+      <c r="A70" s="127"/>
       <c r="B70" s="15"/>
-      <c r="C70" s="131"/>
+      <c r="C70" s="128"/>
       <c r="D70" s="43"/>
       <c r="E70" s="43"/>
-      <c r="F70" s="108"/>
-      <c r="G70" s="132"/>
-      <c r="H70" s="132"/>
-      <c r="I70" s="132"/>
+      <c r="F70" s="105"/>
+      <c r="G70" s="129"/>
+      <c r="H70" s="129"/>
+      <c r="I70" s="129"/>
       <c r="J70" s="6"/>
-      <c r="K70" s="133"/>
+      <c r="K70" s="130"/>
       <c r="L70" s="37"/>
       <c r="M70" s="37"/>
       <c r="P70" s="19"/>
     </row>
     <row r="71" spans="1:16" hidden="1">
-      <c r="A71" s="130"/>
+      <c r="A71" s="127"/>
       <c r="B71" s="15"/>
-      <c r="C71" s="131"/>
+      <c r="C71" s="128"/>
       <c r="D71" s="43"/>
       <c r="E71" s="43"/>
-      <c r="F71" s="108"/>
-      <c r="G71" s="132"/>
-      <c r="H71" s="132"/>
-      <c r="I71" s="132"/>
+      <c r="F71" s="105"/>
+      <c r="G71" s="129"/>
+      <c r="H71" s="129"/>
+      <c r="I71" s="129"/>
       <c r="J71" s="6"/>
-      <c r="K71" s="133"/>
+      <c r="K71" s="130"/>
       <c r="L71" s="37"/>
       <c r="M71" s="37"/>
       <c r="P71" s="19"/>
     </row>
     <row r="72" spans="1:16" hidden="1">
-      <c r="A72" s="130"/>
+      <c r="A72" s="127"/>
       <c r="B72" s="15"/>
-      <c r="C72" s="141"/>
+      <c r="C72" s="138"/>
       <c r="D72" s="43"/>
       <c r="E72" s="43"/>
-      <c r="F72" s="108"/>
-      <c r="G72" s="132"/>
-      <c r="H72" s="132"/>
-      <c r="I72" s="132"/>
+      <c r="F72" s="105"/>
+      <c r="G72" s="129"/>
+      <c r="H72" s="129"/>
+      <c r="I72" s="129"/>
       <c r="J72" s="6"/>
-      <c r="K72" s="133"/>
-      <c r="L72" s="135"/>
+      <c r="K72" s="130"/>
+      <c r="L72" s="132"/>
       <c r="M72" s="37"/>
       <c r="P72" s="19"/>
     </row>
     <row r="73" spans="1:16" hidden="1">
-      <c r="A73" s="130"/>
+      <c r="A73" s="127"/>
       <c r="B73" s="15"/>
-      <c r="C73" s="131"/>
+      <c r="C73" s="128"/>
       <c r="D73" s="43"/>
       <c r="E73" s="43"/>
-      <c r="F73" s="108"/>
-      <c r="G73" s="132"/>
-      <c r="H73" s="132"/>
-      <c r="I73" s="132"/>
+      <c r="F73" s="105"/>
+      <c r="G73" s="129"/>
+      <c r="H73" s="129"/>
+      <c r="I73" s="129"/>
       <c r="J73" s="6"/>
-      <c r="K73" s="133"/>
+      <c r="K73" s="130"/>
       <c r="L73" s="37"/>
       <c r="M73" s="37"/>
       <c r="P73" s="19"/>
     </row>
     <row r="74" spans="1:16" hidden="1">
-      <c r="A74" s="130"/>
+      <c r="A74" s="127"/>
       <c r="B74" s="15"/>
-      <c r="C74" s="131"/>
+      <c r="C74" s="128"/>
       <c r="D74" s="43"/>
       <c r="E74" s="43"/>
-      <c r="F74" s="108"/>
-      <c r="G74" s="132"/>
-      <c r="H74" s="132"/>
-      <c r="I74" s="132"/>
+      <c r="F74" s="105"/>
+      <c r="G74" s="129"/>
+      <c r="H74" s="129"/>
+      <c r="I74" s="129"/>
       <c r="J74" s="6"/>
-      <c r="K74" s="133"/>
+      <c r="K74" s="130"/>
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
       <c r="P74" s="19"/>
     </row>
     <row r="75" spans="1:16">
-      <c r="A75" s="113"/>
+      <c r="A75" s="110"/>
       <c r="B75" s="45"/>
-      <c r="C75" s="142"/>
+      <c r="C75" s="139"/>
       <c r="D75" s="46"/>
       <c r="E75" s="46"/>
-      <c r="F75" s="143"/>
-      <c r="G75" s="144"/>
-      <c r="H75" s="144"/>
-      <c r="I75" s="144"/>
+      <c r="F75" s="140"/>
+      <c r="G75" s="141"/>
+      <c r="H75" s="141"/>
+      <c r="I75" s="141"/>
       <c r="J75" s="8"/>
       <c r="K75" s="50"/>
       <c r="L75" s="50"/>
       <c r="M75" s="50"/>
-      <c r="P75" s="118"/>
+      <c r="P75" s="115"/>
     </row>
     <row r="76" spans="1:16">
       <c r="B76" s="51"/>
-      <c r="G76" s="145"/>
-      <c r="H76" s="145"/>
-      <c r="I76" s="145"/>
-      <c r="J76" s="146"/>
+      <c r="G76" s="142"/>
+      <c r="H76" s="142"/>
+      <c r="I76" s="142"/>
+      <c r="J76" s="143"/>
     </row>
     <row r="77" spans="1:16" ht="15" thickBot="1">
       <c r="B77" s="51"/>
-      <c r="G77" s="147">
+      <c r="G77" s="144">
         <f>SUM(G$9:G$75)</f>
         <v>0</v>
       </c>
-      <c r="H77" s="147">
+      <c r="H77" s="144">
         <f t="shared" ref="H77:I77" si="0">SUM(H$9:H$75)</f>
         <v>0</v>
       </c>
-      <c r="I77" s="147">
+      <c r="I77" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J77" s="148"/>
+      <c r="J77" s="145"/>
       <c r="K77" s="54">
         <f>SUM(G77:I77)</f>
         <v>0</v>
@@ -8536,7 +8530,7 @@
       <c r="G78" s="12"/>
       <c r="H78" s="12"/>
       <c r="I78" s="12"/>
-      <c r="J78" s="146"/>
+      <c r="J78" s="143"/>
     </row>
     <row r="79" spans="1:16" s="19" customFormat="1">
       <c r="G79" s="54"/>
@@ -8572,283 +8566,283 @@
     <col min="10" max="10" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="150" customFormat="1" ht="25.2">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:10" s="147" customFormat="1" ht="25.2">
+      <c r="A1" s="146" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="154" customFormat="1" ht="25.2">
-      <c r="A2" s="151" t="s">
+    <row r="2" spans="1:10" s="151" customFormat="1" ht="25.2">
+      <c r="A2" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-    </row>
-    <row r="3" spans="1:10" s="154" customFormat="1" ht="25.8" thickBot="1">
-      <c r="A3" s="151" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+    </row>
+    <row r="3" spans="1:10" s="151" customFormat="1" ht="25.8" thickBot="1">
+      <c r="A3" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="155">
+      <c r="D3" s="152">
         <v>46023</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="82.2" thickBot="1">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="153" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="158" t="s">
+      <c r="D4" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="158" t="s">
+      <c r="F4" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="158" t="s">
+      <c r="G4" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="159" t="s">
+      <c r="I4" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="160"/>
+      <c r="J4" s="157"/>
     </row>
     <row r="5" spans="1:10" ht="17.399999999999999">
-      <c r="A5" s="161"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
+      <c r="A5" s="158"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
     </row>
     <row r="6" spans="1:10" ht="17.399999999999999">
-      <c r="A6" s="165"/>
-      <c r="B6" s="166"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="168"/>
-      <c r="E6" s="168"/>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="168"/>
+      <c r="A6" s="162"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
     </row>
     <row r="7" spans="1:10" ht="17.399999999999999">
-      <c r="A7" s="165"/>
-      <c r="B7" s="166"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
+      <c r="A7" s="162"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
     </row>
     <row r="8" spans="1:10" ht="17.399999999999999">
-      <c r="A8" s="165"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="168"/>
-      <c r="E8" s="168"/>
-      <c r="F8" s="168"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
-      <c r="I8" s="168"/>
+      <c r="A8" s="162"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
     </row>
     <row r="9" spans="1:10" ht="17.399999999999999">
-      <c r="A9" s="165"/>
-      <c r="B9" s="166"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="168"/>
-      <c r="I9" s="168"/>
+      <c r="A9" s="162"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
     </row>
     <row r="10" spans="1:10" ht="17.399999999999999">
-      <c r="A10" s="165"/>
-      <c r="B10" s="166"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="168"/>
+      <c r="A10" s="162"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="164"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
     </row>
     <row r="11" spans="1:10" ht="17.399999999999999">
-      <c r="A11" s="165"/>
-      <c r="B11" s="166"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="168"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="168"/>
-      <c r="I11" s="168"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
     </row>
     <row r="12" spans="1:10" ht="17.399999999999999">
-      <c r="A12" s="165"/>
-      <c r="B12" s="166"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="168"/>
-      <c r="F12" s="168"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="168"/>
-      <c r="I12" s="168"/>
+      <c r="A12" s="162"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
     </row>
     <row r="13" spans="1:10" ht="17.399999999999999">
-      <c r="A13" s="165"/>
-      <c r="B13" s="166"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="168"/>
-      <c r="H13" s="168"/>
-      <c r="I13" s="168"/>
+      <c r="A13" s="162"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
     </row>
     <row r="14" spans="1:10" ht="17.399999999999999">
-      <c r="A14" s="165"/>
-      <c r="B14" s="166"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="168"/>
-      <c r="F14" s="168"/>
-      <c r="G14" s="168"/>
-      <c r="H14" s="168"/>
-      <c r="I14" s="168"/>
+      <c r="A14" s="162"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="165"/>
     </row>
     <row r="15" spans="1:10" ht="17.399999999999999">
-      <c r="A15" s="165"/>
-      <c r="B15" s="166"/>
-      <c r="C15" s="167"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="168"/>
+      <c r="A15" s="162"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="165"/>
+      <c r="I15" s="165"/>
     </row>
     <row r="16" spans="1:10" ht="17.399999999999999">
-      <c r="A16" s="165"/>
-      <c r="B16" s="166"/>
-      <c r="C16" s="167"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="168"/>
+      <c r="A16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="165"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="165"/>
+      <c r="I16" s="165"/>
     </row>
     <row r="17" spans="1:10" ht="17.399999999999999">
-      <c r="A17" s="165"/>
-      <c r="B17" s="166"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="168"/>
-      <c r="H17" s="168"/>
-      <c r="I17" s="168"/>
+      <c r="A17" s="162"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="165"/>
+      <c r="H17" s="165"/>
+      <c r="I17" s="165"/>
     </row>
     <row r="18" spans="1:10" ht="17.399999999999999">
-      <c r="A18" s="165"/>
-      <c r="B18" s="166"/>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="168"/>
-      <c r="H18" s="168"/>
-      <c r="I18" s="168"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="165"/>
+      <c r="H18" s="165"/>
+      <c r="I18" s="165"/>
     </row>
     <row r="19" spans="1:10" ht="17.399999999999999">
-      <c r="A19" s="169"/>
-      <c r="B19" s="166"/>
-      <c r="C19" s="167"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="168"/>
-      <c r="H19" s="168"/>
-      <c r="I19" s="168"/>
+      <c r="A19" s="166"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="165"/>
+      <c r="I19" s="165"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="170"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="173"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="168"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="170"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
     </row>
     <row r="21" spans="1:10" ht="14.4" thickBot="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="177"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="177"/>
-      <c r="H21" s="177"/>
-      <c r="I21" s="177"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="172"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="174"/>
     </row>
     <row r="22" spans="1:10" ht="21" thickBot="1">
-      <c r="A22" s="178" t="s">
+      <c r="A22" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="179">
+      <c r="B22" s="176">
         <f>SUM(B5:B21)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="180">
+      <c r="C22" s="177">
         <f t="shared" ref="C22:I22" si="0">SUM(C5:C21)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="181">
+      <c r="D22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="181">
+      <c r="E22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="181">
+      <c r="G22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="181">
+      <c r="H22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="182">
+      <c r="I22" s="179">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="183">
+      <c r="J22" s="180">
         <f>SUM(C22:I22)</f>
         <v>0</v>
       </c>
@@ -8875,287 +8869,287 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="150" customFormat="1" ht="25.2">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:10" s="147" customFormat="1" ht="25.2">
+      <c r="A1" s="146" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="154" customFormat="1" ht="25.2">
-      <c r="A2" s="151" t="s">
+    <row r="2" spans="1:10" s="151" customFormat="1" ht="25.2">
+      <c r="A2" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-    </row>
-    <row r="3" spans="1:10" s="154" customFormat="1" ht="25.8" thickBot="1">
-      <c r="A3" s="151" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+    </row>
+    <row r="3" spans="1:10" s="151" customFormat="1" ht="25.8" thickBot="1">
+      <c r="A3" s="148" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="184">
+      <c r="D3" s="181">
         <v>45962</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="82.2" thickBot="1">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="185" t="s">
+      <c r="C4" s="182" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="158" t="s">
+      <c r="D4" s="155" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="158" t="s">
+      <c r="E4" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="158" t="s">
+      <c r="F4" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="158" t="s">
+      <c r="G4" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="158" t="s">
+      <c r="H4" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="159" t="s">
+      <c r="I4" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="160"/>
+      <c r="J4" s="157"/>
     </row>
     <row r="5" spans="1:10" ht="17.399999999999999">
-      <c r="A5" s="161"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
+      <c r="A5" s="158"/>
+      <c r="B5" s="159"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
+      <c r="I5" s="161"/>
     </row>
     <row r="6" spans="1:10" ht="17.399999999999999">
-      <c r="A6" s="165"/>
-      <c r="B6" s="166"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="168"/>
-      <c r="E6" s="168"/>
-      <c r="F6" s="168"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="168"/>
+      <c r="A6" s="162"/>
+      <c r="B6" s="163"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="165"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="165"/>
     </row>
     <row r="7" spans="1:10" ht="17.399999999999999">
-      <c r="A7" s="165"/>
-      <c r="B7" s="166"/>
-      <c r="C7" s="167"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
+      <c r="A7" s="162"/>
+      <c r="B7" s="163"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="165"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="165"/>
     </row>
     <row r="8" spans="1:10" ht="17.399999999999999">
-      <c r="A8" s="165"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="168"/>
-      <c r="E8" s="168"/>
-      <c r="F8" s="168"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
-      <c r="I8" s="168"/>
+      <c r="A8" s="162"/>
+      <c r="B8" s="163"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
     </row>
     <row r="9" spans="1:10" ht="17.399999999999999">
-      <c r="A9" s="165"/>
-      <c r="B9" s="166"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="168"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="168"/>
-      <c r="I9" s="168"/>
+      <c r="A9" s="162"/>
+      <c r="B9" s="163"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
     </row>
     <row r="10" spans="1:10" ht="17.399999999999999">
-      <c r="A10" s="165"/>
-      <c r="B10" s="166"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="168"/>
+      <c r="A10" s="162"/>
+      <c r="B10" s="163"/>
+      <c r="C10" s="164"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
     </row>
     <row r="11" spans="1:10" ht="17.399999999999999">
-      <c r="A11" s="165"/>
-      <c r="B11" s="166"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="168"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="168"/>
-      <c r="I11" s="168"/>
+      <c r="A11" s="162"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
     </row>
     <row r="12" spans="1:10" ht="17.399999999999999">
-      <c r="A12" s="165"/>
-      <c r="B12" s="166"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="168"/>
-      <c r="F12" s="168"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="168"/>
-      <c r="I12" s="168"/>
+      <c r="A12" s="162"/>
+      <c r="B12" s="163"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
     </row>
     <row r="13" spans="1:10" ht="17.399999999999999">
-      <c r="A13" s="165"/>
-      <c r="B13" s="166"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="168"/>
-      <c r="H13" s="168"/>
-      <c r="I13" s="168"/>
+      <c r="A13" s="162"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
     </row>
     <row r="14" spans="1:10" ht="17.399999999999999">
-      <c r="A14" s="165"/>
-      <c r="B14" s="166"/>
-      <c r="C14" s="167"/>
-      <c r="D14" s="168"/>
-      <c r="E14" s="168"/>
-      <c r="F14" s="168"/>
-      <c r="G14" s="168"/>
-      <c r="H14" s="168"/>
-      <c r="I14" s="168"/>
+      <c r="A14" s="162"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="165"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="165"/>
+      <c r="I14" s="165"/>
     </row>
     <row r="15" spans="1:10" ht="17.399999999999999">
-      <c r="A15" s="165"/>
-      <c r="B15" s="166"/>
-      <c r="C15" s="166"/>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="168"/>
-      <c r="I15" s="168"/>
+      <c r="A15" s="162"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="163"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="165"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="165"/>
+      <c r="I15" s="165"/>
     </row>
     <row r="16" spans="1:10" ht="17.399999999999999">
-      <c r="A16" s="165"/>
-      <c r="B16" s="166"/>
-      <c r="C16" s="166"/>
-      <c r="D16" s="168"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
-      <c r="I16" s="168"/>
+      <c r="A16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="163"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="165"/>
+      <c r="F16" s="165"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="165"/>
+      <c r="I16" s="165"/>
     </row>
     <row r="17" spans="1:11" ht="17.399999999999999">
-      <c r="A17" s="165"/>
-      <c r="B17" s="166"/>
-      <c r="C17" s="167"/>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="168"/>
-      <c r="H17" s="168"/>
-      <c r="I17" s="168"/>
+      <c r="A17" s="162"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="165"/>
+      <c r="H17" s="165"/>
+      <c r="I17" s="165"/>
     </row>
     <row r="18" spans="1:11" ht="17.399999999999999">
-      <c r="A18" s="165"/>
-      <c r="B18" s="166"/>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="168"/>
-      <c r="H18" s="168"/>
-      <c r="I18" s="168"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="163"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="165"/>
+      <c r="H18" s="165"/>
+      <c r="I18" s="165"/>
     </row>
     <row r="19" spans="1:11" ht="17.399999999999999">
-      <c r="A19" s="169"/>
-      <c r="B19" s="166"/>
-      <c r="C19" s="167"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="168"/>
-      <c r="H19" s="168"/>
-      <c r="I19" s="168"/>
+      <c r="A19" s="166"/>
+      <c r="B19" s="163"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="165"/>
+      <c r="I19" s="165"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="170"/>
-      <c r="B20" s="171"/>
-      <c r="C20" s="172"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="173"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="168"/>
+      <c r="C20" s="169"/>
+      <c r="D20" s="170"/>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
     </row>
     <row r="21" spans="1:11" ht="14.4" thickBot="1">
-      <c r="A21" s="174"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="177"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="177"/>
-      <c r="H21" s="177"/>
-      <c r="I21" s="177"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="172"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="174"/>
+      <c r="I21" s="174"/>
     </row>
     <row r="22" spans="1:11" ht="21" thickBot="1">
-      <c r="A22" s="178" t="s">
+      <c r="A22" s="175" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="186">
+      <c r="B22" s="183">
         <f t="shared" ref="B22:H22" si="0">SUM(B5:B21)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="180">
+      <c r="C22" s="177">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D22" s="181">
+      <c r="D22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="181">
+      <c r="E22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="181">
+      <c r="F22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="181">
+      <c r="G22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="181">
+      <c r="H22" s="178">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="182">
+      <c r="I22" s="179">
         <f t="shared" ref="I22" si="1">SUM(I5:I21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="187">
+      <c r="J22" s="184">
         <f>SUM(C22:I22)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="188">
+      <c r="K22" s="185">
         <f>SUM(B22-J22)</f>
         <v>0</v>
       </c>
